--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C259"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,205 +396,205 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>133</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>114</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>132</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>483</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11">
-        <v>945</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>87</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>260</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>228</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>645</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -605,659 +605,659 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>141</v>
+        <v>307</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>170</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>142</v>
+        <v>308</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>170</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>143</v>
+        <v>335</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>179</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>145</v>
+        <v>336</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>180</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>146</v>
+        <v>344</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>177</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>152</v>
+        <v>378</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>141</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>159</v>
+        <v>409</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>828</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>161</v>
+        <v>410</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>167</v>
+        <v>411</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>258</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>168</v>
+        <v>412</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>169</v>
+        <v>413</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>246</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>170</v>
+        <v>424</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C34">
-        <v>419</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>201</v>
+        <v>434</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>205</v>
+        <v>435</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>123</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>214</v>
+        <v>436</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>758</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>216</v>
+        <v>491</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>305</v>
+        <v>590</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>307</v>
+        <v>615</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>308</v>
+        <v>616</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>334</v>
+        <v>641</v>
       </c>
       <c r="B42">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>335</v>
+        <v>823</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>1491</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>336</v>
+        <v>922</v>
       </c>
       <c r="B44">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>128</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>345</v>
+        <v>944</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C45">
-        <v>361</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>361</v>
+        <v>947</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>362</v>
+        <v>955</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>413</v>
+        <v>972</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>95</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>424</v>
+        <v>974</v>
       </c>
       <c r="B49">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>434</v>
+        <v>996</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>435</v>
+        <v>998</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>116</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>436</v>
+        <v>1006</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>491</v>
+        <v>1051</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>590</v>
+        <v>1120</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>112</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>616</v>
+        <v>1309</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>121</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>738</v>
+        <v>1413</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>880</v>
+        <v>1414</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>944</v>
+        <v>1429</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>947</v>
+        <v>1519</v>
       </c>
       <c r="B59">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>47</v>
+        <v>975</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>996</v>
+        <v>1622</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1006</v>
+        <v>1654</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>260</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1080</v>
+        <v>1776</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>162</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1082</v>
+        <v>1801</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1120</v>
+        <v>1895</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>130</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1124</v>
+        <v>2054</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>208</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1163</v>
+        <v>2057</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>402</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1309</v>
+        <v>2104</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>63</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1413</v>
+        <v>2108</v>
       </c>
       <c r="B68">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1414</v>
+        <v>2109</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>115</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1429</v>
+        <v>2160</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>151</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1492</v>
+        <v>2188</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1504</v>
+        <v>2217</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1519</v>
+        <v>2328</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>1890</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1599</v>
+        <v>2336</v>
       </c>
       <c r="B74">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1602</v>
+        <v>2424</v>
       </c>
       <c r="B75">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>1604</v>
+        <v>2436</v>
       </c>
       <c r="B76">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>1622</v>
+        <v>2486</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>1661</v>
+        <v>2726</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>244</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>1766</v>
+        <v>2728</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>1776</v>
+        <v>2730</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>7</v>
@@ -1265,285 +1265,285 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>1777</v>
+        <v>2778</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>126</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>1801</v>
+        <v>2859</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C82">
-        <v>115</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>1813</v>
+        <v>2912</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>88</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2049</v>
+        <v>2991</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84">
-        <v>627</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2103</v>
+        <v>3341</v>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>386</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2104</v>
+        <v>3429</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C86">
-        <v>389</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2109</v>
+        <v>3430</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C87">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2188</v>
+        <v>3454</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>952</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2328</v>
+        <v>3456</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2336</v>
+        <v>3475</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>671</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2422</v>
+        <v>3495</v>
       </c>
       <c r="B91">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>220</v>
+        <v>595</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>2424</v>
+        <v>3610</v>
       </c>
       <c r="B92">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="C92">
-        <v>194</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>2438</v>
+        <v>3671</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>745</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>2497</v>
+        <v>3673</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>2731</v>
+        <v>3892</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>102</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>2735</v>
+        <v>3893</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>59</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>2744</v>
+        <v>4019</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>2776</v>
+        <v>4043</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>164</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>2836</v>
+        <v>4063</v>
       </c>
       <c r="B99">
         <v>3</v>
       </c>
       <c r="C99">
-        <v>423</v>
+        <v>323</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>2859</v>
+        <v>4178</v>
       </c>
       <c r="B100">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C100">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>2879</v>
+        <v>4372</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C101">
-        <v>42</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>2912</v>
+        <v>4672</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>3048</v>
+        <v>5083</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>341</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>3049</v>
+        <v>5153</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>3429</v>
+        <v>5208</v>
       </c>
       <c r="B105">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>63</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>3454</v>
+        <v>5243</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -1551,32 +1551,32 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>3462</v>
+        <v>5341</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>3475</v>
+        <v>5342</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C108">
-        <v>70</v>
+        <v>338</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>3478</v>
+        <v>5343</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -1584,43 +1584,43 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>3495</v>
+        <v>5490</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>3670</v>
+        <v>5493</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>289</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>3673</v>
+        <v>5577</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>299</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>3900</v>
+        <v>5646</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>7</v>
@@ -1628,21 +1628,21 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>3955</v>
+        <v>5723</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>3961</v>
+        <v>5733</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -1650,54 +1650,54 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>4715</v>
+        <v>5946</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>4960</v>
+        <v>6097</v>
       </c>
       <c r="B117">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="C117">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5020</v>
+        <v>6098</v>
       </c>
       <c r="B118">
+        <v>29</v>
+      </c>
+      <c r="C118">
         <v>23</v>
-      </c>
-      <c r="C118">
-        <v>596</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5081</v>
+        <v>6575</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5086</v>
+        <v>6928</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,252 +1705,252 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5151</v>
+        <v>6935</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5152</v>
+        <v>6936</v>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5165</v>
+        <v>7007</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>5208</v>
+        <v>7324</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>648</v>
+        <v>47</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>5243</v>
+        <v>7457</v>
       </c>
       <c r="B125">
         <v>3</v>
       </c>
       <c r="C125">
-        <v>294</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>5341</v>
+        <v>7520</v>
       </c>
       <c r="B126">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>5342</v>
+        <v>7567</v>
       </c>
       <c r="B127">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>5343</v>
+        <v>7885</v>
       </c>
       <c r="B128">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>5577</v>
+        <v>8104</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>245</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>5584</v>
+        <v>8157</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>5647</v>
+        <v>8216</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>72</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>5656</v>
+        <v>8274</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>64</v>
+        <v>462</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>5723</v>
+        <v>8283</v>
       </c>
       <c r="B133">
         <v>2</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6072</v>
+        <v>8284</v>
       </c>
       <c r="B134">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>39</v>
+        <v>279</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>6575</v>
+        <v>8557</v>
       </c>
       <c r="B135">
         <v>3</v>
       </c>
       <c r="C135">
-        <v>297</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>6965</v>
+        <v>8635</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136">
-        <v>46</v>
+        <v>462</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>6968</v>
+        <v>8648</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>44</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>7005</v>
+        <v>8649</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>7204</v>
+        <v>8675</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>427</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>7520</v>
+        <v>8676</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>166</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>7885</v>
+        <v>8677</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141">
-        <v>158</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>7886</v>
+        <v>8690</v>
       </c>
       <c r="B142">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>161</v>
+        <v>478</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8058</v>
+        <v>8853</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,131 +1958,131 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8106</v>
+        <v>8897</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>8216</v>
+        <v>8923</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8283</v>
+        <v>8927</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C146">
-        <v>552</v>
+        <v>491</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8648</v>
+        <v>8944</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8650</v>
+        <v>9069</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8676</v>
+        <v>9087</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C149">
-        <v>329</v>
+        <v>104</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>8677</v>
+        <v>9087</v>
       </c>
       <c r="B150">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C150">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8754</v>
+        <v>9691</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>403</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8915</v>
+        <v>9827</v>
       </c>
       <c r="B152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8927</v>
+        <v>9828</v>
       </c>
       <c r="B153">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>15</v>
+        <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>8938</v>
+        <v>10149</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>185</v>
+        <v>551</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>8939</v>
+        <v>10170</v>
       </c>
       <c r="B155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -2090,76 +2090,76 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>8943</v>
+        <v>10409</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>444</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>8990</v>
+        <v>10514</v>
       </c>
       <c r="B157">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9081</v>
+        <v>10529</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C158">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9083</v>
+        <v>10536</v>
       </c>
       <c r="B159">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>566</v>
+        <v>184</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9085</v>
+        <v>10716</v>
       </c>
       <c r="B160">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C160">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9087</v>
+        <v>10717</v>
       </c>
       <c r="B161">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C161">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9087</v>
+        <v>10780</v>
       </c>
       <c r="B162">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C162">
         <v>7</v>
@@ -2167,359 +2167,359 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9239</v>
+        <v>10825</v>
       </c>
       <c r="B163">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C163">
-        <v>7</v>
+        <v>398</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>9507</v>
+        <v>11090</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>9611</v>
+        <v>11093</v>
       </c>
       <c r="B165">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C165">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>9787</v>
+        <v>11116</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>9829</v>
+        <v>11158</v>
       </c>
       <c r="B167">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C167">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>9877</v>
+        <v>11215</v>
       </c>
       <c r="B168">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C168">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>10080</v>
+        <v>11396</v>
       </c>
       <c r="B169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C169">
-        <v>134</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>10149</v>
+        <v>11404</v>
       </c>
       <c r="B170">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C170">
-        <v>1048</v>
+        <v>64</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>10407</v>
+        <v>11467</v>
       </c>
       <c r="B171">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C171">
-        <v>1290</v>
+        <v>58</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>10516</v>
+        <v>11489</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C172">
-        <v>690</v>
+        <v>62</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>10524</v>
+        <v>11490</v>
       </c>
       <c r="B173">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>10616</v>
+        <v>11491</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>10716</v>
+        <v>11504</v>
       </c>
       <c r="B175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>10780</v>
+        <v>11510</v>
       </c>
       <c r="B176">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C176">
-        <v>7</v>
+        <v>348</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11059</v>
+        <v>11526</v>
       </c>
       <c r="B177">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11081</v>
+        <v>11583</v>
       </c>
       <c r="B178">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C178">
-        <v>424</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11089</v>
+        <v>11610</v>
       </c>
       <c r="B179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C179">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11131</v>
+        <v>11684</v>
       </c>
       <c r="B180">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C180">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11216</v>
+        <v>11738</v>
       </c>
       <c r="B181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181">
-        <v>89</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11399</v>
+        <v>11739</v>
       </c>
       <c r="B182">
         <v>2</v>
       </c>
       <c r="C182">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11467</v>
+        <v>11813</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11504</v>
+        <v>11856</v>
       </c>
       <c r="B184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184">
-        <v>157</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11510</v>
+        <v>11914</v>
       </c>
       <c r="B185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C185">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11555</v>
+        <v>11952</v>
       </c>
       <c r="B186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11687</v>
+        <v>12058</v>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C187">
-        <v>351</v>
+        <v>168</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11737</v>
+        <v>12059</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>7</v>
+        <v>170</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11767</v>
+        <v>12343</v>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189">
-        <v>191</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11793</v>
+        <v>12417</v>
       </c>
       <c r="B190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>11846</v>
+        <v>12479</v>
       </c>
       <c r="B191">
         <v>3</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>372</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>11848</v>
+        <v>12573</v>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>11854</v>
+        <v>12764</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193">
-        <v>117</v>
+        <v>426</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>11868</v>
+        <v>12858</v>
       </c>
       <c r="B194">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C194">
-        <v>337</v>
+        <v>555</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>11895</v>
+        <v>12887</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -2530,62 +2530,62 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>11952</v>
+        <v>12923</v>
       </c>
       <c r="B196">
         <v>1</v>
       </c>
       <c r="C196">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12010</v>
+        <v>12924</v>
       </c>
       <c r="B197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C197">
-        <v>173</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>12059</v>
+        <v>12964</v>
       </c>
       <c r="B198">
         <v>3</v>
       </c>
       <c r="C198">
-        <v>7</v>
+        <v>238</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>12128</v>
+        <v>13023</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>793</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>12347</v>
+        <v>13034</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C200">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>12350</v>
+        <v>13167</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -2596,274 +2596,274 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>12573</v>
+        <v>13249</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C202">
-        <v>7</v>
+        <v>96</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>12661</v>
+        <v>13260</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>12923</v>
+        <v>18964</v>
       </c>
       <c r="B204">
         <v>1</v>
       </c>
       <c r="C204">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>12925</v>
+        <v>19047</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C205">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13023</v>
+        <v>20498</v>
       </c>
       <c r="B206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C206">
-        <v>10</v>
+        <v>96</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13028</v>
+        <v>20969</v>
       </c>
       <c r="B207">
         <v>3</v>
       </c>
       <c r="C207">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13249</v>
+        <v>21068</v>
       </c>
       <c r="B208">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C208">
-        <v>32</v>
+        <v>299</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>13259</v>
+        <v>21088</v>
       </c>
       <c r="B209">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C209">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>13260</v>
+        <v>21683</v>
       </c>
       <c r="B210">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C210">
-        <v>83</v>
+        <v>352</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>13264</v>
+        <v>21686</v>
       </c>
       <c r="B211">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>83</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>13276</v>
+        <v>21694</v>
       </c>
       <c r="B212">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C212">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>13281</v>
+        <v>21699</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C213">
-        <v>7</v>
+        <v>139</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>13286</v>
+        <v>22316</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C214">
-        <v>377</v>
+        <v>183</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>13293</v>
+        <v>22317</v>
       </c>
       <c r="B215">
         <v>3</v>
       </c>
       <c r="C215">
-        <v>342</v>
+        <v>182</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>13299</v>
+        <v>22565</v>
       </c>
       <c r="B216">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>173</v>
+        <v>793</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>13403</v>
+        <v>23489</v>
       </c>
       <c r="B217">
         <v>3</v>
       </c>
       <c r="C217">
-        <v>8</v>
+        <v>123</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>13965</v>
+        <v>23491</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>13968</v>
+        <v>23492</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C219">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>14037</v>
+        <v>23493</v>
       </c>
       <c r="B220">
         <v>3</v>
       </c>
       <c r="C220">
-        <v>395</v>
+        <v>123</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>14038</v>
+        <v>23494</v>
       </c>
       <c r="B221">
         <v>3</v>
       </c>
       <c r="C221">
-        <v>330</v>
+        <v>123</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>14039</v>
+        <v>23611</v>
       </c>
       <c r="B222">
         <v>3</v>
       </c>
       <c r="C222">
-        <v>319</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>19583</v>
+        <v>23961</v>
       </c>
       <c r="B223">
         <v>3</v>
       </c>
       <c r="C223">
-        <v>7</v>
+        <v>185</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>19971</v>
+        <v>23992</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C224">
-        <v>436</v>
+        <v>40</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>19987</v>
+        <v>24127</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>20650</v>
+        <v>24243</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C226">
         <v>7</v>
@@ -2871,40 +2871,40 @@
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>21068</v>
+        <v>24252</v>
       </c>
       <c r="B227">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C227">
-        <v>613</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>21088</v>
+        <v>24257</v>
       </c>
       <c r="B228">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>21703</v>
+        <v>24260</v>
       </c>
       <c r="B229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>21798</v>
+        <v>24566</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>21807</v>
+        <v>24712</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C231">
-        <v>116</v>
+        <v>363</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>21810</v>
+        <v>24756</v>
       </c>
       <c r="B232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C232">
-        <v>7</v>
+        <v>238</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>21946</v>
+        <v>24844</v>
       </c>
       <c r="B233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C233">
         <v>7</v>
@@ -2948,288 +2948,24 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>22317</v>
+        <v>24889</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>22554</v>
+        <v>25278</v>
       </c>
       <c r="B235">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C235">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236">
-        <v>22565</v>
-      </c>
-      <c r="B236">
-        <v>3</v>
-      </c>
-      <c r="C236">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237">
-        <v>22590</v>
-      </c>
-      <c r="B237">
-        <v>1</v>
-      </c>
-      <c r="C237">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238">
-        <v>22634</v>
-      </c>
-      <c r="B238">
-        <v>2</v>
-      </c>
-      <c r="C238">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239">
-        <v>22667</v>
-      </c>
-      <c r="B239">
-        <v>2</v>
-      </c>
-      <c r="C239">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240">
-        <v>22925</v>
-      </c>
-      <c r="B240">
-        <v>3</v>
-      </c>
-      <c r="C240">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241">
-        <v>23231</v>
-      </c>
-      <c r="B241">
-        <v>3</v>
-      </c>
-      <c r="C241">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242">
-        <v>23235</v>
-      </c>
-      <c r="B242">
-        <v>25</v>
-      </c>
-      <c r="C242">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>23278</v>
-      </c>
-      <c r="B243">
-        <v>3</v>
-      </c>
-      <c r="C243">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>23335</v>
-      </c>
-      <c r="B244">
-        <v>14</v>
-      </c>
-      <c r="C244">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>23489</v>
-      </c>
-      <c r="B245">
-        <v>3</v>
-      </c>
-      <c r="C245">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>23491</v>
-      </c>
-      <c r="B246">
-        <v>3</v>
-      </c>
-      <c r="C246">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>23492</v>
-      </c>
-      <c r="B247">
-        <v>3</v>
-      </c>
-      <c r="C247">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248">
-        <v>23493</v>
-      </c>
-      <c r="B248">
-        <v>3</v>
-      </c>
-      <c r="C248">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249">
-        <v>23494</v>
-      </c>
-      <c r="B249">
-        <v>3</v>
-      </c>
-      <c r="C249">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250">
-        <v>23599</v>
-      </c>
-      <c r="B250">
-        <v>10</v>
-      </c>
-      <c r="C250">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251">
-        <v>23611</v>
-      </c>
-      <c r="B251">
-        <v>3</v>
-      </c>
-      <c r="C251">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252">
-        <v>23960</v>
-      </c>
-      <c r="B252">
-        <v>3</v>
-      </c>
-      <c r="C252">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3">
-      <c r="A253">
-        <v>24127</v>
-      </c>
-      <c r="B253">
-        <v>3</v>
-      </c>
-      <c r="C253">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3">
-      <c r="A254">
-        <v>24252</v>
-      </c>
-      <c r="B254">
-        <v>1</v>
-      </c>
-      <c r="C254">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
-      <c r="A255">
-        <v>24257</v>
-      </c>
-      <c r="B255">
-        <v>1</v>
-      </c>
-      <c r="C255">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
-      <c r="A256">
-        <v>24260</v>
-      </c>
-      <c r="B256">
-        <v>1</v>
-      </c>
-      <c r="C256">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
-      <c r="A257">
-        <v>24708</v>
-      </c>
-      <c r="B257">
-        <v>3</v>
-      </c>
-      <c r="C257">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
-      <c r="A258">
-        <v>25344</v>
-      </c>
-      <c r="B258">
-        <v>3</v>
-      </c>
-      <c r="C258">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
-      <c r="A259">
-        <v>25960</v>
-      </c>
-      <c r="B259">
-        <v>2</v>
-      </c>
-      <c r="C259">
-        <v>7</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C250"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,989 +396,989 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>64</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>204</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>140</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>946</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>862</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>380</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>30</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>307</v>
+        <v>159</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>199</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>308</v>
+        <v>161</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>94</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>335</v>
+        <v>167</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23">
-        <v>756</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>65</v>
+        <v>541</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>346</v>
+        <v>170</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>67</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>378</v>
+        <v>214</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>245</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>409</v>
+        <v>216</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>412</v>
+        <v>217</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>434</v>
+        <v>248</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>435</v>
+        <v>307</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>470</v>
+        <v>308</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>615</v>
+        <v>336</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>616</v>
+        <v>345</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>59</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>624</v>
+        <v>361</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>641</v>
+        <v>362</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>823</v>
+        <v>409</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>947</v>
+        <v>412</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>949</v>
+        <v>413</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>950</v>
+        <v>434</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>951</v>
+        <v>435</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>965</v>
+        <v>436</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>974</v>
+        <v>470</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1055</v>
+        <v>515</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C44">
-        <v>21</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1059</v>
+        <v>589</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>39</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1082</v>
+        <v>590</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C46">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1084</v>
+        <v>615</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>1087</v>
+        <v>624</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>1091</v>
+        <v>641</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>1120</v>
+        <v>823</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>1124</v>
+        <v>950</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>1126</v>
+        <v>965</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>1243</v>
+        <v>990</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>1309</v>
+        <v>996</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>32</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1413</v>
+        <v>1055</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1414</v>
+        <v>1082</v>
       </c>
       <c r="B56">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>58</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1429</v>
+        <v>1126</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1447</v>
+        <v>1243</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1448</v>
+        <v>1309</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1492</v>
+        <v>1413</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1504</v>
+        <v>1414</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>223</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1598</v>
+        <v>1429</v>
       </c>
       <c r="B62">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1599</v>
+        <v>1447</v>
       </c>
       <c r="B63">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1622</v>
+        <v>1448</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1654</v>
+        <v>1598</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C65">
-        <v>53</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1655</v>
+        <v>1599</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1656</v>
+        <v>1601</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1691</v>
+        <v>1622</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1703</v>
+        <v>1655</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>222</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2103</v>
+        <v>1656</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2104</v>
+        <v>1776</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>198</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2108</v>
+        <v>1777</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>156</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2109</v>
+        <v>2049</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>22</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2190</v>
+        <v>2054</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>25</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2322</v>
+        <v>2055</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2328</v>
+        <v>2103</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C76">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2335</v>
+        <v>2109</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>262</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2336</v>
+        <v>2328</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>343</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2422</v>
+        <v>2335</v>
       </c>
       <c r="B79">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>107</v>
+        <v>265</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2424</v>
+        <v>2336</v>
       </c>
       <c r="B80">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>133</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2436</v>
+        <v>2423</v>
       </c>
       <c r="B81">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C81">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2497</v>
+        <v>2424</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2508</v>
+        <v>2436</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2537</v>
+        <v>2703</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="B85">
         <v>3</v>
       </c>
       <c r="C85">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2774</v>
+        <v>2735</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>224</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2778</v>
+        <v>2774</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>9</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2878</v>
+        <v>2912</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2912</v>
+        <v>3429</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C89">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2935</v>
+        <v>3434</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2990</v>
+        <v>3454</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -1386,252 +1386,252 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>3016</v>
+        <v>3475</v>
       </c>
       <c r="B92">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>3049</v>
+        <v>3670</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>3429</v>
+        <v>3673</v>
       </c>
       <c r="B94">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>31</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3434</v>
+        <v>3674</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3454</v>
+        <v>3893</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3475</v>
+        <v>3900</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>3477</v>
+        <v>3955</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>3478</v>
+        <v>4019</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>3670</v>
+        <v>4063</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>316</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>3671</v>
+        <v>4178</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C101">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>3673</v>
+        <v>4222</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C102">
-        <v>141</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>3674</v>
+        <v>4672</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>183</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>3889</v>
+        <v>4867</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>153</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>3891</v>
+        <v>4880</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C105">
-        <v>154</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>3899</v>
+        <v>4901</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>3955</v>
+        <v>5005</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>4019</v>
+        <v>5081</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>4063</v>
+        <v>5083</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>325</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>4178</v>
+        <v>5151</v>
       </c>
       <c r="B110">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>137</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>4222</v>
+        <v>5152</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>4672</v>
+        <v>5153</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>4715</v>
+        <v>5165</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>4728</v>
+        <v>5343</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -1639,329 +1639,329 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>4867</v>
+        <v>5434</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>4880</v>
+        <v>5490</v>
       </c>
       <c r="B116">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>4882</v>
+        <v>5491</v>
       </c>
       <c r="B117">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>4901</v>
+        <v>5493</v>
       </c>
       <c r="B118">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>4955</v>
+        <v>5494</v>
       </c>
       <c r="B119">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5005</v>
+        <v>5584</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>78</v>
+        <v>145</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5121</v>
+        <v>5723</v>
       </c>
       <c r="B121">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5152</v>
+        <v>5733</v>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5153</v>
+        <v>6013</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C123">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>5165</v>
+        <v>6097</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>5208</v>
+        <v>6097</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C125">
-        <v>328</v>
+        <v>93</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>5209</v>
+        <v>6098</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>328</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>5343</v>
+        <v>6494</v>
       </c>
       <c r="B127">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>5490</v>
+        <v>6496</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>59</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>5491</v>
+        <v>6630</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>5493</v>
+        <v>6927</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C130">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>5494</v>
+        <v>6928</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C131">
-        <v>59</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>5513</v>
+        <v>6929</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>5577</v>
+        <v>6935</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>354</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>5584</v>
+        <v>7084</v>
       </c>
       <c r="B134">
         <v>3</v>
       </c>
       <c r="C134">
-        <v>142</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>5646</v>
+        <v>7318</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C135">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>5658</v>
+        <v>7457</v>
       </c>
       <c r="B136">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>5723</v>
+        <v>7520</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>5733</v>
+        <v>7885</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>6013</v>
+        <v>7886</v>
       </c>
       <c r="B139">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C139">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>6072</v>
+        <v>7887</v>
       </c>
       <c r="B140">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>8</v>
+        <v>106</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>6097</v>
+        <v>8055</v>
       </c>
       <c r="B141">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>6097</v>
+        <v>8104</v>
       </c>
       <c r="B142">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>53</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>6098</v>
+        <v>8106</v>
       </c>
       <c r="B143">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>6494</v>
+        <v>8157</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C144">
         <v>30</v>
@@ -1969,98 +1969,98 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>6496</v>
+        <v>8274</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>23</v>
+        <v>446</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>6927</v>
+        <v>8648</v>
       </c>
       <c r="B146">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>245</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>6928</v>
+        <v>8650</v>
       </c>
       <c r="B147">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>245</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>6929</v>
+        <v>8651</v>
       </c>
       <c r="B148">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>7007</v>
+        <v>8675</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>47</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>7084</v>
+        <v>8676</v>
       </c>
       <c r="B150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>167</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>7318</v>
+        <v>8685</v>
       </c>
       <c r="B151">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>9</v>
+        <v>111</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>7367</v>
+        <v>8853</v>
       </c>
       <c r="B152">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>7518</v>
+        <v>8898</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153">
         <v>7</v>
@@ -2068,131 +2068,131 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>7520</v>
+        <v>8915</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>7885</v>
+        <v>8938</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C155">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>7886</v>
+        <v>8945</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>83</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>7887</v>
+        <v>8990</v>
       </c>
       <c r="B157">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C157">
-        <v>104</v>
+        <v>63</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>8055</v>
+        <v>9081</v>
       </c>
       <c r="B158">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C158">
-        <v>7</v>
+        <v>646</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>8104</v>
+        <v>9085</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C159">
-        <v>264</v>
+        <v>73</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>8155</v>
+        <v>9087</v>
       </c>
       <c r="B160">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C160">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>8157</v>
+        <v>9208</v>
       </c>
       <c r="B161">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C161">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>8216</v>
+        <v>9209</v>
       </c>
       <c r="B162">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C162">
-        <v>1223</v>
+        <v>56</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>8635</v>
+        <v>9239</v>
       </c>
       <c r="B163">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C163">
-        <v>201</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>8685</v>
+        <v>9358</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>8853</v>
+        <v>9507</v>
       </c>
       <c r="B165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C165">
         <v>7</v>
@@ -2200,703 +2200,703 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>8915</v>
+        <v>9760</v>
       </c>
       <c r="B166">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C166">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>8926</v>
+        <v>9784</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>8990</v>
+        <v>9833</v>
       </c>
       <c r="B168">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C168">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>9069</v>
+        <v>9960</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>9081</v>
+        <v>10105</v>
       </c>
       <c r="B170">
         <v>3</v>
       </c>
       <c r="C170">
-        <v>654</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>9085</v>
+        <v>10149</v>
       </c>
       <c r="B171">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>91</v>
+        <v>556</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>9288</v>
+        <v>10170</v>
       </c>
       <c r="B172">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C172">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>9358</v>
+        <v>10275</v>
       </c>
       <c r="B173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C173">
-        <v>33</v>
+        <v>108</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>9691</v>
+        <v>10524</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C174">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>9784</v>
+        <v>10616</v>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>9785</v>
+        <v>10721</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C176">
-        <v>104</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>9787</v>
+        <v>10780</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>9827</v>
+        <v>10825</v>
       </c>
       <c r="B178">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C178">
-        <v>7</v>
+        <v>897</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>9833</v>
+        <v>11059</v>
       </c>
       <c r="B179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C179">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>9910</v>
+        <v>11116</v>
       </c>
       <c r="B180">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C180">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>9960</v>
+        <v>11150</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>10105</v>
+        <v>11290</v>
       </c>
       <c r="B182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C182">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>10170</v>
+        <v>11396</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183">
-        <v>31</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>10524</v>
+        <v>11471</v>
       </c>
       <c r="B184">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C184">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>10529</v>
+        <v>11493</v>
       </c>
       <c r="B185">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C185">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>10574</v>
+        <v>11555</v>
       </c>
       <c r="B186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186">
-        <v>316</v>
+        <v>75</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>10616</v>
+        <v>11681</v>
       </c>
       <c r="B187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>51</v>
+        <v>360</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>10721</v>
+        <v>11895</v>
       </c>
       <c r="B188">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C188">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>10825</v>
+        <v>11914</v>
       </c>
       <c r="B189">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C189">
-        <v>398</v>
+        <v>46</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11039</v>
+        <v>12128</v>
       </c>
       <c r="B190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190">
-        <v>141</v>
+        <v>26</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>11059</v>
+        <v>12304</v>
       </c>
       <c r="B191">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>11092</v>
+        <v>12535</v>
       </c>
       <c r="B192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C192">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>11093</v>
+        <v>12539</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>11116</v>
+        <v>12598</v>
       </c>
       <c r="B194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>11216</v>
+        <v>12621</v>
       </c>
       <c r="B195">
         <v>1</v>
       </c>
       <c r="C195">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>11290</v>
+        <v>12661</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C196">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>11404</v>
+        <v>12662</v>
       </c>
       <c r="B197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C197">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>11471</v>
+        <v>12722</v>
       </c>
       <c r="B198">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C198">
-        <v>8</v>
+        <v>166</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>11491</v>
+        <v>12764</v>
       </c>
       <c r="B199">
         <v>2</v>
       </c>
       <c r="C199">
-        <v>81</v>
+        <v>434</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>11493</v>
+        <v>12923</v>
       </c>
       <c r="B200">
         <v>1</v>
       </c>
       <c r="C200">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>11555</v>
+        <v>12924</v>
       </c>
       <c r="B201">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>11583</v>
+        <v>12925</v>
       </c>
       <c r="B202">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C202">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>11685</v>
+        <v>13249</v>
       </c>
       <c r="B203">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C203">
-        <v>254</v>
+        <v>36</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>11739</v>
+        <v>13256</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C204">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>11894</v>
+        <v>13257</v>
       </c>
       <c r="B205">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C205">
-        <v>73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>11895</v>
+        <v>13258</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>11914</v>
+        <v>13258</v>
       </c>
       <c r="B207">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C207">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>11952</v>
+        <v>13259</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C208">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>12128</v>
+        <v>13264</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C209">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>12535</v>
+        <v>13269</v>
       </c>
       <c r="B210">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C210">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>12539</v>
+        <v>13271</v>
       </c>
       <c r="B211">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C211">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>12546</v>
+        <v>13272</v>
       </c>
       <c r="B212">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C212">
-        <v>25</v>
+        <v>132</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>12598</v>
+        <v>13276</v>
       </c>
       <c r="B213">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C213">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>12621</v>
+        <v>13280</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>498</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>12661</v>
+        <v>13403</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>46</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>12791</v>
+        <v>13467</v>
       </c>
       <c r="B216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216">
-        <v>458</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>12923</v>
+        <v>14037</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C217">
-        <v>22</v>
+        <v>200</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>12924</v>
+        <v>19987</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>12925</v>
+        <v>20208</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C219">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>13028</v>
+        <v>20650</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C220">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>13249</v>
+        <v>20927</v>
       </c>
       <c r="B221">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>13258</v>
+        <v>21068</v>
       </c>
       <c r="B222">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C222">
-        <v>60</v>
+        <v>304</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>13271</v>
+        <v>21088</v>
       </c>
       <c r="B223">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C223">
-        <v>13</v>
+        <v>127</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>13293</v>
+        <v>21454</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C224">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>13403</v>
+        <v>22089</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C225">
-        <v>84</v>
+        <v>123</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>19987</v>
+        <v>22316</v>
       </c>
       <c r="B226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C226">
-        <v>37</v>
+        <v>183</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>20208</v>
+        <v>22566</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C227">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>20486</v>
+        <v>22631</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C228">
-        <v>7</v>
+        <v>431</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>20650</v>
+        <v>22665</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229">
         <v>7</v>
@@ -2904,84 +2904,84 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>20977</v>
+        <v>23493</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C230">
-        <v>22</v>
+        <v>124</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>21068</v>
+        <v>23992</v>
       </c>
       <c r="B231">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C231">
-        <v>304</v>
+        <v>40</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>21088</v>
+        <v>24125</v>
       </c>
       <c r="B232">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C232">
-        <v>123</v>
+        <v>16</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>22089</v>
+        <v>24127</v>
       </c>
       <c r="B233">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C233">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>22317</v>
+        <v>24252</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C234">
-        <v>182</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>22327</v>
+        <v>24258</v>
       </c>
       <c r="B235">
         <v>1</v>
       </c>
       <c r="C235">
-        <v>8</v>
+        <v>241</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>22631</v>
+        <v>24260</v>
       </c>
       <c r="B236">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C236">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>22665</v>
+        <v>24705</v>
       </c>
       <c r="B237">
         <v>2</v>
@@ -2992,145 +2992,46 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>22667</v>
+        <v>25278</v>
       </c>
       <c r="B238">
         <v>2</v>
       </c>
       <c r="C238">
-        <v>15</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>23493</v>
+        <v>25286</v>
       </c>
       <c r="B239">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>121</v>
+        <v>15</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>23992</v>
+        <v>25899</v>
       </c>
       <c r="B240">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C240">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>24126</v>
+        <v>25960</v>
       </c>
       <c r="B241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C241">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242">
-        <v>24127</v>
-      </c>
-      <c r="B242">
-        <v>3</v>
-      </c>
-      <c r="C242">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>24252</v>
-      </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>24260</v>
-      </c>
-      <c r="B244">
-        <v>1</v>
-      </c>
-      <c r="C244">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>24707</v>
-      </c>
-      <c r="B245">
-        <v>3</v>
-      </c>
-      <c r="C245">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>25278</v>
-      </c>
-      <c r="B246">
-        <v>2</v>
-      </c>
-      <c r="C246">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>25286</v>
-      </c>
-      <c r="B247">
-        <v>1</v>
-      </c>
-      <c r="C247">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248">
-        <v>25342</v>
-      </c>
-      <c r="B248">
-        <v>3</v>
-      </c>
-      <c r="C248">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249">
-        <v>25899</v>
-      </c>
-      <c r="B249">
-        <v>2</v>
-      </c>
-      <c r="C249">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250">
-        <v>25958</v>
-      </c>
-      <c r="B250">
-        <v>2</v>
-      </c>
-      <c r="C250">
-        <v>358</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C251"/>
+  <dimension ref="A1:C243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,285 +396,285 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>73</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>672</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>118</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>118</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>38</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>93</v>
+        <v>885</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>129</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>305</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>214</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>616</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>221</v>
+        <v>307</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -682,106 +682,106 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>248</v>
+        <v>335</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>32</v>
+        <v>739</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>85</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>125</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>56</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>361</v>
+        <v>409</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34">
-        <v>245</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -792,57 +792,57 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>515</v>
+        <v>470</v>
       </c>
       <c r="B41">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>119</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>202</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -858,90 +858,90 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>624</v>
+        <v>593</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>77</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>790</v>
+        <v>823</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>926</v>
+        <v>947</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -957,35 +957,35 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>1007</v>
+        <v>990</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>155</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -996,40 +996,40 @@
         <v>7</v>
       </c>
       <c r="C56">
-        <v>763</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1087</v>
+        <v>1126</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>185</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1124</v>
+        <v>1163</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>107</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1126</v>
+        <v>1243</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>174</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1045,29 +1045,29 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C61">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1413</v>
+        <v>1447</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -1078,219 +1078,219 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1448</v>
+        <v>1490</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1504</v>
+        <v>1492</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1519</v>
+        <v>1598</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>975</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B67">
         <v>68</v>
       </c>
       <c r="C67">
-        <v>203</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1599</v>
+        <v>1622</v>
       </c>
       <c r="B68">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1622</v>
+        <v>1654</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1656</v>
+        <v>1703</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>86</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2054</v>
+        <v>1851</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>274</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2103</v>
+        <v>2050</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>197</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2109</v>
+        <v>2103</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C73">
-        <v>22</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2160</v>
+        <v>2104</v>
       </c>
       <c r="B74">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>319</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2328</v>
+        <v>2108</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2335</v>
+        <v>2109</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>265</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2336</v>
+        <v>2322</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>335</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2422</v>
+        <v>2328</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>249</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2423</v>
+        <v>2335</v>
       </c>
       <c r="B79">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>178</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2424</v>
+        <v>2336</v>
       </c>
       <c r="B80">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>162</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2508</v>
+        <v>2422</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2537</v>
+        <v>2423</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>21</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2539</v>
+        <v>2508</v>
       </c>
       <c r="B83">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>7</v>
@@ -1298,230 +1298,230 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2703</v>
+        <v>2537</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>483</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2774</v>
+        <v>2538</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>96</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2776</v>
+        <v>2726</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2935</v>
+        <v>2728</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2991</v>
+        <v>2774</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>3258</v>
+        <v>2878</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>3429</v>
+        <v>2879</v>
       </c>
       <c r="B90">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>3434</v>
+        <v>2912</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>3454</v>
+        <v>2916</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>3673</v>
+        <v>2934</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>150</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>3674</v>
+        <v>2935</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>144</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3908</v>
+        <v>2991</v>
       </c>
       <c r="B95">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>247</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3955</v>
+        <v>3016</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C96">
-        <v>132</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3961</v>
+        <v>3258</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>63</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>3994</v>
+        <v>3434</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>4019</v>
+        <v>3454</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>4063</v>
+        <v>3475</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>317</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>4178</v>
+        <v>3495</v>
       </c>
       <c r="B101">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>958</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>4672</v>
+        <v>3670</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>4715</v>
+        <v>3671</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>4728</v>
+        <v>3673</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -1529,43 +1529,43 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>4867</v>
+        <v>3674</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>4880</v>
+        <v>3889</v>
       </c>
       <c r="B106">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>4882</v>
+        <v>3891</v>
       </c>
       <c r="B107">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>154</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>4901</v>
+        <v>3909</v>
       </c>
       <c r="B108">
-        <v>332</v>
+        <v>7</v>
       </c>
       <c r="C108">
         <v>8</v>
@@ -1573,167 +1573,167 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>4960</v>
+        <v>3961</v>
       </c>
       <c r="B109">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>4967</v>
+        <v>3994</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5005</v>
+        <v>4019</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>165</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5081</v>
+        <v>4063</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>111</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5083</v>
+        <v>4246</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>73</v>
+        <v>54</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5152</v>
+        <v>4672</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5153</v>
+        <v>4867</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5165</v>
+        <v>4880</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C116">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>5208</v>
+        <v>4882</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C117">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5209</v>
+        <v>4901</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5243</v>
+        <v>5081</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>150</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5341</v>
+        <v>5152</v>
       </c>
       <c r="B120">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5342</v>
+        <v>5153</v>
       </c>
       <c r="B121">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5343</v>
+        <v>5165</v>
       </c>
       <c r="B122">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5452</v>
+        <v>5343</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="C126">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1788,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="C128">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -1799,125 +1799,125 @@
         <v>3</v>
       </c>
       <c r="C129">
-        <v>322</v>
+        <v>141</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>5647</v>
+        <v>5723</v>
       </c>
       <c r="B130">
         <v>2</v>
       </c>
       <c r="C130">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>5723</v>
+        <v>5831</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>5946</v>
+        <v>6098</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C132">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>6013</v>
+        <v>6158</v>
       </c>
       <c r="B133">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6034</v>
+        <v>6494</v>
       </c>
       <c r="B134">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>509</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>6097</v>
+        <v>6496</v>
       </c>
       <c r="B135">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>6097</v>
+        <v>6540</v>
       </c>
       <c r="B136">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C136">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>6098</v>
+        <v>6630</v>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>6496</v>
+        <v>6927</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C138">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>6540</v>
+        <v>6928</v>
       </c>
       <c r="B139">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>6630</v>
+        <v>6929</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C140">
         <v>7</v>
@@ -1925,62 +1925,62 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>6928</v>
+        <v>7318</v>
       </c>
       <c r="B141">
         <v>12</v>
       </c>
       <c r="C141">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>6929</v>
+        <v>7324</v>
       </c>
       <c r="B142">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>7005</v>
+        <v>7367</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C143">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>7204</v>
+        <v>7457</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>23</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>7318</v>
+        <v>7520</v>
       </c>
       <c r="B145">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>7367</v>
+        <v>8055</v>
       </c>
       <c r="B146">
         <v>12</v>
@@ -1991,329 +1991,329 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>7457</v>
+        <v>8104</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>7520</v>
+        <v>8672</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>7886</v>
+        <v>8674</v>
       </c>
       <c r="B149">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>82</v>
+        <v>219</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>7887</v>
+        <v>8675</v>
       </c>
       <c r="B150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>78</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8055</v>
+        <v>8676</v>
       </c>
       <c r="B151">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8104</v>
+        <v>8677</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8106</v>
+        <v>8926</v>
       </c>
       <c r="B153">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>8157</v>
+        <v>8939</v>
       </c>
       <c r="B154">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>8635</v>
+        <v>8990</v>
       </c>
       <c r="B155">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C155">
-        <v>455</v>
+        <v>63</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>8650</v>
+        <v>9069</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>245</v>
+        <v>95</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>8651</v>
+        <v>9070</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>241</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>8674</v>
+        <v>9085</v>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C158">
-        <v>162</v>
+        <v>73</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>8685</v>
+        <v>9208</v>
       </c>
       <c r="B159">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C159">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>8898</v>
+        <v>9209</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C160">
-        <v>386</v>
+        <v>76</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>8926</v>
+        <v>9239</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C161">
-        <v>36</v>
+        <v>114</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>8990</v>
+        <v>9358</v>
       </c>
       <c r="B162">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9070</v>
+        <v>9613</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>9081</v>
+        <v>9691</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>654</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>9085</v>
+        <v>9828</v>
       </c>
       <c r="B165">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C165">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>9208</v>
+        <v>9833</v>
       </c>
       <c r="B166">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C166">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>9209</v>
+        <v>9835</v>
       </c>
       <c r="B167">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C167">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>9239</v>
+        <v>9910</v>
       </c>
       <c r="B168">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C168">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>9531</v>
+        <v>9910</v>
       </c>
       <c r="B169">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C169">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>9760</v>
+        <v>9960</v>
       </c>
       <c r="B170">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C170">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>9784</v>
+        <v>10105</v>
       </c>
       <c r="B171">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>9828</v>
+        <v>10170</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C172">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>9833</v>
+        <v>10524</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C173">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>9910</v>
+        <v>10574</v>
       </c>
       <c r="B174">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C174">
-        <v>21</v>
+        <v>316</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>9960</v>
+        <v>10616</v>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>10105</v>
+        <v>10780</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C176">
         <v>7</v>
@@ -2321,351 +2321,351 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>10170</v>
+        <v>10993</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177">
-        <v>32</v>
+        <v>72</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>10185</v>
+        <v>11039</v>
       </c>
       <c r="B178">
         <v>2</v>
       </c>
       <c r="C178">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>10275</v>
+        <v>11059</v>
       </c>
       <c r="B179">
         <v>3</v>
       </c>
       <c r="C179">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>10616</v>
+        <v>11116</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>10825</v>
+        <v>11150</v>
       </c>
       <c r="B181">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C181">
-        <v>886</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>10993</v>
+        <v>11404</v>
       </c>
       <c r="B182">
         <v>2</v>
       </c>
       <c r="C182">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11059</v>
+        <v>11471</v>
       </c>
       <c r="B183">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C183">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11090</v>
+        <v>11490</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11093</v>
+        <v>11493</v>
       </c>
       <c r="B185">
         <v>1</v>
       </c>
       <c r="C185">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11116</v>
+        <v>11495</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11150</v>
+        <v>11555</v>
       </c>
       <c r="B187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11234</v>
+        <v>11583</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C188">
-        <v>140</v>
+        <v>75</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11290</v>
+        <v>11855</v>
       </c>
       <c r="B189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11396</v>
+        <v>11856</v>
       </c>
       <c r="B190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>11403</v>
+        <v>11895</v>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>11471</v>
+        <v>11952</v>
       </c>
       <c r="B192">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C192">
-        <v>8</v>
+        <v>336</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>11493</v>
+        <v>11961</v>
       </c>
       <c r="B193">
         <v>1</v>
       </c>
       <c r="C193">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>11495</v>
+        <v>12128</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>11685</v>
+        <v>12535</v>
       </c>
       <c r="B195">
         <v>2</v>
       </c>
       <c r="C195">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>11739</v>
+        <v>12539</v>
       </c>
       <c r="B196">
         <v>2</v>
       </c>
       <c r="C196">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>11792</v>
+        <v>12598</v>
       </c>
       <c r="B197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>11855</v>
+        <v>12621</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>11868</v>
+        <v>12661</v>
       </c>
       <c r="B199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C199">
-        <v>377</v>
+        <v>45</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>11895</v>
+        <v>12662</v>
       </c>
       <c r="B200">
         <v>1</v>
       </c>
       <c r="C200">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>11914</v>
+        <v>12722</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C201">
-        <v>46</v>
+        <v>163</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>11967</v>
+        <v>12923</v>
       </c>
       <c r="B202">
         <v>1</v>
       </c>
       <c r="C202">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>12128</v>
+        <v>12924</v>
       </c>
       <c r="B203">
         <v>1</v>
       </c>
       <c r="C203">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>12535</v>
+        <v>12925</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C204">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>12539</v>
+        <v>13249</v>
       </c>
       <c r="B205">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C205">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>12544</v>
+        <v>13256</v>
       </c>
       <c r="B206">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C206">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>12546</v>
+        <v>13258</v>
       </c>
       <c r="B207">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C207">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>12598</v>
+        <v>13259</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C208">
         <v>7</v>
@@ -2673,230 +2673,230 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>12621</v>
+        <v>13260</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C209">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>12764</v>
+        <v>13263</v>
       </c>
       <c r="B210">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C210">
-        <v>440</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>12924</v>
+        <v>13264</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C211">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>12974</v>
+        <v>13269</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C212">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>13249</v>
+        <v>13271</v>
       </c>
       <c r="B213">
         <v>29</v>
       </c>
       <c r="C213">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>13256</v>
+        <v>13272</v>
       </c>
       <c r="B214">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C214">
-        <v>51</v>
+        <v>134</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>13257</v>
+        <v>13274</v>
       </c>
       <c r="B215">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C215">
-        <v>46</v>
+        <v>194</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>13258</v>
+        <v>13276</v>
       </c>
       <c r="B216">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C216">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>13260</v>
+        <v>13293</v>
       </c>
       <c r="B217">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C217">
-        <v>41</v>
+        <v>267</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>13264</v>
+        <v>13403</v>
       </c>
       <c r="B218">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C218">
-        <v>41</v>
+        <v>86</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>13269</v>
+        <v>19987</v>
       </c>
       <c r="B219">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C219">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>13271</v>
+        <v>20208</v>
       </c>
       <c r="B220">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C220">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>13272</v>
+        <v>20650</v>
       </c>
       <c r="B221">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>13276</v>
+        <v>21068</v>
       </c>
       <c r="B222">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C222">
-        <v>8</v>
+        <v>304</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>13403</v>
+        <v>21088</v>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C223">
-        <v>86</v>
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>13467</v>
+        <v>21269</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>7</v>
+        <v>416</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>19047</v>
+        <v>21454</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C225">
-        <v>170</v>
+        <v>21</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>19987</v>
+        <v>22089</v>
       </c>
       <c r="B226">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C226">
-        <v>37</v>
+        <v>120</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>20208</v>
+        <v>22313</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>20486</v>
+        <v>22631</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C228">
-        <v>7</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>20650</v>
+        <v>22665</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229">
         <v>7</v>
@@ -2904,243 +2904,155 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>21068</v>
+        <v>22667</v>
       </c>
       <c r="B230">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C230">
-        <v>308</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>21088</v>
+        <v>23238</v>
       </c>
       <c r="B231">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C231">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>21454</v>
+        <v>23380</v>
       </c>
       <c r="B232">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C232">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>22049</v>
+        <v>23992</v>
       </c>
       <c r="B233">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C233">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>22089</v>
+        <v>24125</v>
       </c>
       <c r="B234">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>22310</v>
+        <v>24127</v>
       </c>
       <c r="B235">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C235">
-        <v>7</v>
+        <v>139</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>22316</v>
+        <v>24252</v>
       </c>
       <c r="B236">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C236">
-        <v>184</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>22631</v>
+        <v>24253</v>
       </c>
       <c r="B237">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C237">
-        <v>428</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>22665</v>
+        <v>24260</v>
       </c>
       <c r="B238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C238">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>23238</v>
+        <v>25278</v>
       </c>
       <c r="B239">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C239">
-        <v>10</v>
+        <v>163</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>23380</v>
+        <v>25286</v>
       </c>
       <c r="B240">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>23489</v>
+        <v>25342</v>
       </c>
       <c r="B241">
         <v>3</v>
       </c>
       <c r="C241">
-        <v>123</v>
+        <v>16</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>23493</v>
+        <v>25344</v>
       </c>
       <c r="B242">
         <v>3</v>
       </c>
       <c r="C242">
-        <v>125</v>
+        <v>73</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>23494</v>
+        <v>25899</v>
       </c>
       <c r="B243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C243">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>23992</v>
-      </c>
-      <c r="B244">
-        <v>29</v>
-      </c>
-      <c r="C244">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>24125</v>
-      </c>
-      <c r="B245">
-        <v>3</v>
-      </c>
-      <c r="C245">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>24252</v>
-      </c>
-      <c r="B246">
-        <v>1</v>
-      </c>
-      <c r="C246">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>24253</v>
-      </c>
-      <c r="B247">
-        <v>1</v>
-      </c>
-      <c r="C247">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248">
-        <v>24707</v>
-      </c>
-      <c r="B248">
-        <v>3</v>
-      </c>
-      <c r="C248">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249">
-        <v>25286</v>
-      </c>
-      <c r="B249">
-        <v>1</v>
-      </c>
-      <c r="C249">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250">
-        <v>25345</v>
-      </c>
-      <c r="B250">
-        <v>3</v>
-      </c>
-      <c r="C250">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251">
-        <v>25899</v>
-      </c>
-      <c r="B251">
-        <v>2</v>
-      </c>
-      <c r="C251">
         <v>50</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C243"/>
+  <dimension ref="A1:C244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,95 +402,95 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>65</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>66</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>165</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -523,89 +523,89 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>129</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>384</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>218</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>885</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -616,337 +616,337 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
       <c r="C22">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>975</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>739</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>336</v>
+        <v>415</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>148</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>187</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>245</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>411</v>
+        <v>590</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>412</v>
+        <v>624</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>414</v>
+        <v>823</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>415</v>
+        <v>926</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>416</v>
+        <v>944</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>434</v>
+        <v>949</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>435</v>
+        <v>952</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>470</v>
+        <v>965</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>524</v>
+        <v>972</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>48</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>590</v>
+        <v>974</v>
       </c>
       <c r="B43">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>56</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>593</v>
+        <v>990</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>132</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>624</v>
+        <v>991</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>823</v>
+        <v>996</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>926</v>
+        <v>1059</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>947</v>
+        <v>1070</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>949</v>
+        <v>1080</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>950</v>
+        <v>1082</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>952</v>
+        <v>1163</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>46</v>
+        <v>462</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>965</v>
+        <v>1447</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -957,10 +957,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>974</v>
+        <v>1448</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -968,348 +968,348 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>990</v>
+        <v>1490</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1059</v>
+        <v>1492</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1070</v>
+        <v>1519</v>
       </c>
       <c r="B56">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>1088</v>
+        <v>975</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1126</v>
+        <v>1598</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C57">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1163</v>
+        <v>1599</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C58">
-        <v>201</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1243</v>
+        <v>1602</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1309</v>
+        <v>1622</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1406</v>
+        <v>1703</v>
       </c>
       <c r="B61">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>48</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1447</v>
+        <v>2054</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1448</v>
+        <v>2055</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>613</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1490</v>
+        <v>2057</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>29</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1492</v>
+        <v>2103</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1598</v>
+        <v>2104</v>
       </c>
       <c r="B66">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>203</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1599</v>
+        <v>2108</v>
       </c>
       <c r="B67">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1622</v>
+        <v>2322</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1654</v>
+        <v>2328</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>69</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1703</v>
+        <v>2335</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>219</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1851</v>
+        <v>2422</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2050</v>
+        <v>2508</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>272</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2103</v>
+        <v>2537</v>
       </c>
       <c r="B73">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>200</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2104</v>
+        <v>2538</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>319</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2108</v>
+        <v>2703</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="C75">
-        <v>343</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2109</v>
+        <v>2726</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2322</v>
+        <v>2774</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>65</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2328</v>
+        <v>2878</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2335</v>
+        <v>2911</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2336</v>
+        <v>2912</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>345</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2422</v>
+        <v>2934</v>
       </c>
       <c r="B81">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>252</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2423</v>
+        <v>2935</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>144</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2508</v>
+        <v>2991</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2537</v>
+        <v>3016</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C84">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2538</v>
+        <v>3258</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -1320,150 +1320,150 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2726</v>
+        <v>3434</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2728</v>
+        <v>3454</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2774</v>
+        <v>3475</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>218</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2878</v>
+        <v>3495</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2879</v>
+        <v>3575</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C90">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2912</v>
+        <v>3673</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>2916</v>
+        <v>3674</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>41</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>2934</v>
+        <v>3896</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C93">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>2935</v>
+        <v>3900</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>2991</v>
+        <v>3994</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>191</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3016</v>
+        <v>4019</v>
       </c>
       <c r="B96">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3258</v>
+        <v>4063</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>23</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>3434</v>
+        <v>4246</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>3454</v>
+        <v>4672</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1474,480 +1474,480 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>3475</v>
+        <v>4715</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>3495</v>
+        <v>4728</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>958</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>3670</v>
+        <v>4867</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>141</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>3671</v>
+        <v>4880</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>3673</v>
+        <v>4882</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>3674</v>
+        <v>4901</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C105">
-        <v>146</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>3889</v>
+        <v>4962</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C106">
-        <v>110</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>3891</v>
+        <v>4967</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>154</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>3909</v>
+        <v>5111</v>
       </c>
       <c r="B108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>3961</v>
+        <v>5152</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>3994</v>
+        <v>5153</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>4019</v>
+        <v>5165</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>4063</v>
+        <v>5343</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C112">
-        <v>317</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>4246</v>
+        <v>5434</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>4672</v>
+        <v>5490</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>4867</v>
+        <v>5491</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>4880</v>
+        <v>5493</v>
       </c>
       <c r="B116">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>4882</v>
+        <v>5494</v>
       </c>
       <c r="B117">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>4901</v>
+        <v>5577</v>
       </c>
       <c r="B118">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5081</v>
+        <v>5584</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C119">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5152</v>
+        <v>5644</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5153</v>
+        <v>5647</v>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5165</v>
+        <v>5723</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5343</v>
+        <v>5831</v>
       </c>
       <c r="B123">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>5490</v>
+        <v>6097</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C124">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>5491</v>
+        <v>6098</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>5493</v>
+        <v>6158</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>77</v>
+        <v>347</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>5494</v>
+        <v>6494</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>5577</v>
+        <v>6496</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>124</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>5584</v>
+        <v>6497</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>141</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>5723</v>
+        <v>6540</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C130">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>5831</v>
+        <v>6575</v>
       </c>
       <c r="B131">
         <v>3</v>
       </c>
       <c r="C131">
-        <v>20</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>6098</v>
+        <v>6630</v>
       </c>
       <c r="B132">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>6158</v>
+        <v>6927</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C133">
-        <v>153</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6494</v>
+        <v>6928</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>6496</v>
+        <v>6929</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C135">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>6540</v>
+        <v>7007</v>
       </c>
       <c r="B136">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>103</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>6630</v>
+        <v>7204</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>6927</v>
+        <v>7318</v>
       </c>
       <c r="B138">
         <v>12</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>6928</v>
+        <v>7367</v>
       </c>
       <c r="B139">
         <v>12</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>6929</v>
+        <v>7457</v>
       </c>
       <c r="B140">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>7318</v>
+        <v>7520</v>
       </c>
       <c r="B141">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>7324</v>
+        <v>7558</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>7367</v>
+        <v>8055</v>
       </c>
       <c r="B143">
         <v>12</v>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>7457</v>
+        <v>8104</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>134</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>7520</v>
+        <v>8106</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -1980,183 +1980,183 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8055</v>
+        <v>8157</v>
       </c>
       <c r="B146">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8104</v>
+        <v>8926</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8672</v>
+        <v>8939</v>
       </c>
       <c r="B148">
         <v>2</v>
       </c>
       <c r="C148">
-        <v>165</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8674</v>
+        <v>8990</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C149">
-        <v>219</v>
+        <v>63</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>8675</v>
+        <v>9069</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>165</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8676</v>
+        <v>9070</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>165</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8677</v>
+        <v>9081</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152">
-        <v>9</v>
+        <v>654</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8926</v>
+        <v>9208</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C153">
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>8939</v>
+        <v>9209</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>8990</v>
+        <v>9239</v>
       </c>
       <c r="B155">
         <v>25</v>
       </c>
       <c r="C155">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>9069</v>
+        <v>9289</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C156">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>9070</v>
+        <v>9828</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9085</v>
+        <v>9830</v>
       </c>
       <c r="B158">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C158">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9208</v>
+        <v>9835</v>
       </c>
       <c r="B159">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C159">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9209</v>
+        <v>9910</v>
       </c>
       <c r="B160">
         <v>25</v>
       </c>
       <c r="C160">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9239</v>
+        <v>9910</v>
       </c>
       <c r="B161">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C161">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9358</v>
+        <v>9960</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2167,95 +2167,95 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9613</v>
+        <v>10105</v>
       </c>
       <c r="B163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C163">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>9691</v>
+        <v>10149</v>
       </c>
       <c r="B164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C164">
-        <v>101</v>
+        <v>547</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>9828</v>
+        <v>10170</v>
       </c>
       <c r="B165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C165">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>9833</v>
+        <v>10524</v>
       </c>
       <c r="B166">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C166">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>9835</v>
+        <v>10530</v>
       </c>
       <c r="B167">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C167">
-        <v>96</v>
+        <v>36</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>9910</v>
+        <v>10616</v>
       </c>
       <c r="B168">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C168">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>9910</v>
+        <v>10716</v>
       </c>
       <c r="B169">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C169">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>9960</v>
+        <v>10780</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C170">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>10105</v>
+        <v>11059</v>
       </c>
       <c r="B171">
         <v>3</v>
@@ -2266,186 +2266,186 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>10170</v>
+        <v>11092</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>10524</v>
+        <v>11093</v>
       </c>
       <c r="B173">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>10574</v>
+        <v>11116</v>
       </c>
       <c r="B174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>316</v>
+        <v>46</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>10616</v>
+        <v>11150</v>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175">
-        <v>60</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>10780</v>
+        <v>11216</v>
       </c>
       <c r="B176">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>10993</v>
+        <v>11290</v>
       </c>
       <c r="B177">
         <v>2</v>
       </c>
       <c r="C177">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11039</v>
+        <v>11403</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11059</v>
+        <v>11471</v>
       </c>
       <c r="B179">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C179">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11116</v>
+        <v>11490</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11150</v>
+        <v>11493</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11404</v>
+        <v>11495</v>
       </c>
       <c r="B182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11471</v>
+        <v>11583</v>
       </c>
       <c r="B183">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C183">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11490</v>
+        <v>11793</v>
       </c>
       <c r="B184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11493</v>
+        <v>11855</v>
       </c>
       <c r="B185">
         <v>1</v>
       </c>
       <c r="C185">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11495</v>
+        <v>11856</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11555</v>
+        <v>11868</v>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C187">
-        <v>77</v>
+        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11583</v>
+        <v>11894</v>
       </c>
       <c r="B188">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C188">
         <v>75</v>
@@ -2453,90 +2453,90 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11855</v>
+        <v>11895</v>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11856</v>
+        <v>11952</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190">
-        <v>58</v>
+        <v>147</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>11895</v>
+        <v>11961</v>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>11952</v>
+        <v>12128</v>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>336</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>11961</v>
+        <v>12535</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>12128</v>
+        <v>12539</v>
       </c>
       <c r="B194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12535</v>
+        <v>12544</v>
       </c>
       <c r="B195">
         <v>2</v>
       </c>
       <c r="C195">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12539</v>
+        <v>12546</v>
       </c>
       <c r="B196">
         <v>2</v>
       </c>
       <c r="C196">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -2569,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="C199">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -2580,18 +2580,18 @@
         <v>1</v>
       </c>
       <c r="C200">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>12722</v>
+        <v>12764</v>
       </c>
       <c r="B201">
         <v>2</v>
       </c>
       <c r="C201">
-        <v>163</v>
+        <v>420</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2624,48 +2624,48 @@
         <v>1</v>
       </c>
       <c r="C204">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>13249</v>
+        <v>13116</v>
       </c>
       <c r="B205">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C205">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13256</v>
+        <v>13249</v>
       </c>
       <c r="B206">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C206">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13258</v>
+        <v>13256</v>
       </c>
       <c r="B207">
         <v>25</v>
       </c>
       <c r="C207">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13259</v>
+        <v>13263</v>
       </c>
       <c r="B208">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C208">
         <v>7</v>
@@ -2673,255 +2673,255 @@
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>13260</v>
+        <v>13269</v>
       </c>
       <c r="B209">
         <v>29</v>
       </c>
       <c r="C209">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>13263</v>
+        <v>13271</v>
       </c>
       <c r="B210">
         <v>29</v>
       </c>
       <c r="C210">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>13264</v>
+        <v>13272</v>
       </c>
       <c r="B211">
         <v>29</v>
       </c>
       <c r="C211">
-        <v>42</v>
+        <v>77</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>13269</v>
+        <v>13274</v>
       </c>
       <c r="B212">
         <v>29</v>
       </c>
       <c r="C212">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>13271</v>
+        <v>13276</v>
       </c>
       <c r="B213">
         <v>29</v>
       </c>
       <c r="C213">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>13272</v>
+        <v>13280</v>
       </c>
       <c r="B214">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>134</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>13274</v>
+        <v>13403</v>
       </c>
       <c r="B215">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>194</v>
+        <v>87</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>13276</v>
+        <v>13467</v>
       </c>
       <c r="B216">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C216">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>13293</v>
+        <v>19987</v>
       </c>
       <c r="B217">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C217">
-        <v>267</v>
+        <v>37</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>13403</v>
+        <v>20208</v>
       </c>
       <c r="B218">
         <v>3</v>
       </c>
       <c r="C218">
-        <v>86</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>19987</v>
+        <v>20650</v>
       </c>
       <c r="B219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>20208</v>
+        <v>21068</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>7</v>
+        <v>309</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>20650</v>
+        <v>21088</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C221">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>21068</v>
+        <v>21269</v>
       </c>
       <c r="B222">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>304</v>
+        <v>397</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>21088</v>
+        <v>21454</v>
       </c>
       <c r="B223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>21269</v>
+        <v>22089</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C224">
-        <v>416</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>21454</v>
+        <v>22317</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>22089</v>
+        <v>22631</v>
       </c>
       <c r="B226">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C226">
-        <v>120</v>
+        <v>423</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>22313</v>
+        <v>22665</v>
       </c>
       <c r="B227">
         <v>2</v>
       </c>
       <c r="C227">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>22631</v>
+        <v>22667</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C228">
-        <v>420</v>
+        <v>14</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>22665</v>
+        <v>23234</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C229">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>22667</v>
+        <v>23238</v>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C230">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>23238</v>
+        <v>23335</v>
       </c>
       <c r="B231">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C231">
-        <v>35</v>
+        <v>216</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -2937,43 +2937,43 @@
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>23992</v>
+        <v>23961</v>
       </c>
       <c r="B233">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C233">
-        <v>40</v>
+        <v>417</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>24125</v>
+        <v>23992</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C234">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>24127</v>
+        <v>24125</v>
       </c>
       <c r="B235">
         <v>3</v>
       </c>
       <c r="C235">
-        <v>139</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>24252</v>
+        <v>24127</v>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C236">
         <v>7</v>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>24253</v>
+        <v>24252</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -2992,68 +2992,79 @@
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>24260</v>
+        <v>24253</v>
       </c>
       <c r="B238">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>25278</v>
+        <v>24256</v>
       </c>
       <c r="B239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>25286</v>
+        <v>24258</v>
       </c>
       <c r="B240">
         <v>1</v>
       </c>
       <c r="C240">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>25342</v>
+        <v>25278</v>
       </c>
       <c r="B241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C241">
-        <v>16</v>
+        <v>217</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>25344</v>
+        <v>25286</v>
       </c>
       <c r="B242">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C242">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>25899</v>
+        <v>25342</v>
       </c>
       <c r="B243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C243">
-        <v>50</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <v>25344</v>
+      </c>
+      <c r="B244">
+        <v>3</v>
+      </c>
+      <c r="C244">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C244"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,989 +396,989 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>149</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>149</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>287</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>673</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>129</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>384</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>458</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>18</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20">
-        <v>25</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>23</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>220</v>
+        <v>107</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>307</v>
+        <v>130</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>975</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>345</v>
+        <v>143</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>187</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>409</v>
+        <v>144</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>415</v>
+        <v>145</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>81</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>416</v>
+        <v>151</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>113</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>434</v>
+        <v>159</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>435</v>
+        <v>167</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>470</v>
+        <v>168</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>27</v>
+        <v>482</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>590</v>
+        <v>170</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>130</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>624</v>
+        <v>192</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>59</v>
+        <v>913</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>823</v>
+        <v>201</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>926</v>
+        <v>211</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>944</v>
+        <v>214</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>26</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>949</v>
+        <v>220</v>
       </c>
       <c r="B39">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>952</v>
+        <v>248</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>965</v>
+        <v>308</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>972</v>
+        <v>335</v>
       </c>
       <c r="B42">
         <v>3</v>
       </c>
       <c r="C42">
-        <v>340</v>
+        <v>773</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>974</v>
+        <v>336</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>85</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>990</v>
+        <v>361</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>70</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>991</v>
+        <v>362</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>996</v>
+        <v>409</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1059</v>
+        <v>410</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>1070</v>
+        <v>413</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>1080</v>
+        <v>415</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>1082</v>
+        <v>416</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>1163</v>
+        <v>417</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>462</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>1447</v>
+        <v>418</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>1448</v>
+        <v>434</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>1490</v>
+        <v>470</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1492</v>
+        <v>523</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>21</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1519</v>
+        <v>524</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>975</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1598</v>
+        <v>590</v>
       </c>
       <c r="B57">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>203</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1599</v>
+        <v>615</v>
       </c>
       <c r="B58">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1602</v>
+        <v>616</v>
       </c>
       <c r="B59">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1622</v>
+        <v>823</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1703</v>
+        <v>944</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>216</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2054</v>
+        <v>947</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C62">
-        <v>267</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>2055</v>
+        <v>949</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>613</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2057</v>
+        <v>950</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>261</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2103</v>
+        <v>972</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>363</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2104</v>
+        <v>990</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2108</v>
+        <v>991</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>340</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2322</v>
+        <v>1006</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>65</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2328</v>
+        <v>1056</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>176</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2335</v>
+        <v>1070</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2422</v>
+        <v>1080</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>249</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2508</v>
+        <v>1082</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2537</v>
+        <v>1084</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2538</v>
+        <v>1087</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2703</v>
+        <v>1309</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2726</v>
+        <v>1448</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2774</v>
+        <v>1490</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>158</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2878</v>
+        <v>1492</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2911</v>
+        <v>1599</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C79">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2912</v>
+        <v>1622</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>28</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2934</v>
+        <v>1777</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2935</v>
+        <v>1801</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2991</v>
+        <v>2049</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="C83">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>3016</v>
+        <v>2057</v>
       </c>
       <c r="B84">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>3258</v>
+        <v>2104</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>3434</v>
+        <v>2108</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>53</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>3454</v>
+        <v>2109</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>3475</v>
+        <v>2322</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>3495</v>
+        <v>2328</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>24</v>
+        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>3575</v>
+        <v>2331</v>
       </c>
       <c r="B90">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>3673</v>
+        <v>2335</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
         <v>7</v>
@@ -1386,230 +1386,230 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>3674</v>
+        <v>2537</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>147</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>3896</v>
+        <v>2774</v>
       </c>
       <c r="B93">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>3900</v>
+        <v>2878</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3994</v>
+        <v>2911</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>62</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>4019</v>
+        <v>2912</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>4063</v>
+        <v>2935</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>317</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>4246</v>
+        <v>3454</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>4672</v>
+        <v>3478</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>4715</v>
+        <v>3674</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>4728</v>
+        <v>3889</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>4867</v>
+        <v>3900</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>4880</v>
+        <v>3955</v>
       </c>
       <c r="B103">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>4882</v>
+        <v>4019</v>
       </c>
       <c r="B104">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>4901</v>
+        <v>4063</v>
       </c>
       <c r="B105">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>318</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>4962</v>
+        <v>4246</v>
       </c>
       <c r="B106">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>4967</v>
+        <v>4867</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>5111</v>
+        <v>4901</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C108">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5152</v>
+        <v>5005</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>5153</v>
+        <v>5081</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>14</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5165</v>
+        <v>5083</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5343</v>
+        <v>5152</v>
       </c>
       <c r="B112">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -1617,123 +1617,123 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5434</v>
+        <v>5153</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5490</v>
+        <v>5165</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5491</v>
+        <v>5343</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5493</v>
+        <v>5435</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>5494</v>
+        <v>5490</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5577</v>
+        <v>5491</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>126</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5584</v>
+        <v>5493</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5644</v>
+        <v>5494</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5647</v>
+        <v>5584</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>37</v>
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5723</v>
+        <v>5644</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5831</v>
+        <v>5723</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -1741,32 +1741,32 @@
         <v>6097</v>
       </c>
       <c r="B124">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>6098</v>
+        <v>6097</v>
       </c>
       <c r="B125">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C125">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>6158</v>
+        <v>6098</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>347</v>
+        <v>45</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1777,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="C127">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1788,81 +1788,81 @@
         <v>1</v>
       </c>
       <c r="C128">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>6497</v>
+        <v>6540</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C129">
-        <v>22</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>6540</v>
+        <v>6927</v>
       </c>
       <c r="B130">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C130">
-        <v>100</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>6575</v>
+        <v>6929</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C131">
-        <v>155</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>6630</v>
+        <v>6936</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>62</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>6927</v>
+        <v>7004</v>
       </c>
       <c r="B133">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6928</v>
+        <v>7005</v>
       </c>
       <c r="B134">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>6929</v>
+        <v>7036</v>
       </c>
       <c r="B135">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -1870,10 +1870,10 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>7007</v>
+        <v>7084</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C136">
         <v>103</v>
@@ -1881,68 +1881,68 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>7204</v>
+        <v>7318</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C137">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>7318</v>
+        <v>7457</v>
       </c>
       <c r="B138">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>9</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>7367</v>
+        <v>7520</v>
       </c>
       <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139">
         <v>12</v>
-      </c>
-      <c r="C139">
-        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>7457</v>
+        <v>7885</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>135</v>
+        <v>85</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>7520</v>
+        <v>7886</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>7558</v>
+        <v>7887</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -1975,199 +1975,199 @@
         <v>10</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8157</v>
+        <v>8274</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C146">
-        <v>24</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8926</v>
+        <v>8284</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>37</v>
+        <v>294</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8939</v>
+        <v>8286</v>
       </c>
       <c r="B148">
         <v>2</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>384</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8990</v>
+        <v>8635</v>
       </c>
       <c r="B149">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>63</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>9069</v>
+        <v>8674</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>229</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>9070</v>
+        <v>8675</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>25</v>
+        <v>172</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>9081</v>
+        <v>8677</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152">
-        <v>654</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>9208</v>
+        <v>8898</v>
       </c>
       <c r="B153">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>76</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>9209</v>
+        <v>8915</v>
       </c>
       <c r="B154">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>9239</v>
+        <v>8926</v>
       </c>
       <c r="B155">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>9289</v>
+        <v>8939</v>
       </c>
       <c r="B156">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C156">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>9828</v>
+        <v>8945</v>
       </c>
       <c r="B157">
         <v>3</v>
       </c>
       <c r="C157">
-        <v>7</v>
+        <v>355</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9830</v>
+        <v>8990</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C158">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9835</v>
+        <v>9081</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>95</v>
+        <v>581</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9910</v>
+        <v>9087</v>
       </c>
       <c r="B160">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C160">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9910</v>
+        <v>9208</v>
       </c>
       <c r="B161">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C161">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9960</v>
+        <v>9760</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C162">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>10105</v>
+        <v>9827</v>
       </c>
       <c r="B163">
         <v>3</v>
@@ -2178,282 +2178,282 @@
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>10149</v>
+        <v>9833</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164">
-        <v>547</v>
+        <v>77</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>10170</v>
+        <v>9960</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>10524</v>
+        <v>10105</v>
       </c>
       <c r="B166">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C166">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>10530</v>
+        <v>10149</v>
       </c>
       <c r="B167">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C167">
-        <v>36</v>
+        <v>576</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>10616</v>
+        <v>10170</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>10716</v>
+        <v>10529</v>
       </c>
       <c r="B169">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C169">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>10780</v>
+        <v>10530</v>
       </c>
       <c r="B170">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C170">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>11059</v>
+        <v>10574</v>
       </c>
       <c r="B171">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>7</v>
+        <v>330</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>11092</v>
+        <v>10616</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>11093</v>
+        <v>10716</v>
       </c>
       <c r="B173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C173">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>11116</v>
+        <v>10717</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C174">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>11150</v>
+        <v>10720</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C175">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>11216</v>
+        <v>10825</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C176">
-        <v>46</v>
+        <v>530</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11290</v>
+        <v>10993</v>
       </c>
       <c r="B177">
         <v>2</v>
       </c>
       <c r="C177">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11403</v>
+        <v>11059</v>
       </c>
       <c r="B178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C178">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11471</v>
+        <v>11116</v>
       </c>
       <c r="B179">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C179">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11490</v>
+        <v>11150</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>80</v>
+        <v>27</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11493</v>
+        <v>11403</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11495</v>
+        <v>11404</v>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11583</v>
+        <v>11493</v>
       </c>
       <c r="B183">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C183">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11793</v>
+        <v>11555</v>
       </c>
       <c r="B184">
         <v>2</v>
       </c>
       <c r="C184">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11855</v>
+        <v>11583</v>
       </c>
       <c r="B185">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C185">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11856</v>
+        <v>11687</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186">
-        <v>59</v>
+        <v>245</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11868</v>
+        <v>11895</v>
       </c>
       <c r="B187">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C187">
-        <v>279</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11894</v>
+        <v>11914</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C188">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11895</v>
+        <v>11952</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -2464,40 +2464,40 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11952</v>
+        <v>11961</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190">
-        <v>147</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>11961</v>
+        <v>12128</v>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>12128</v>
+        <v>12535</v>
       </c>
       <c r="B192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C192">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>12535</v>
+        <v>12539</v>
       </c>
       <c r="B193">
         <v>2</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>12539</v>
+        <v>12543</v>
       </c>
       <c r="B194">
         <v>2</v>
@@ -2519,156 +2519,156 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12544</v>
+        <v>12621</v>
       </c>
       <c r="B195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C195">
-        <v>24</v>
+        <v>138</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12546</v>
+        <v>12661</v>
       </c>
       <c r="B196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C196">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12598</v>
+        <v>12764</v>
       </c>
       <c r="B197">
         <v>2</v>
       </c>
       <c r="C197">
-        <v>7</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>12621</v>
+        <v>12870</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>12661</v>
+        <v>12923</v>
       </c>
       <c r="B199">
         <v>1</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>12662</v>
+        <v>12924</v>
       </c>
       <c r="B200">
         <v>1</v>
       </c>
       <c r="C200">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>12764</v>
+        <v>12925</v>
       </c>
       <c r="B201">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>420</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>12923</v>
+        <v>12930</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C202">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>12924</v>
+        <v>13249</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C203">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>12925</v>
+        <v>13256</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C204">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>13116</v>
+        <v>13259</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C205">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13249</v>
+        <v>13260</v>
       </c>
       <c r="B206">
         <v>29</v>
       </c>
       <c r="C206">
-        <v>38</v>
+        <v>86</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13256</v>
+        <v>13263</v>
       </c>
       <c r="B207">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C207">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13263</v>
+        <v>13264</v>
       </c>
       <c r="B208">
         <v>29</v>
       </c>
       <c r="C208">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -2679,103 +2679,103 @@
         <v>29</v>
       </c>
       <c r="C209">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>13271</v>
+        <v>13280</v>
       </c>
       <c r="B210">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C210">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>13272</v>
+        <v>13403</v>
       </c>
       <c r="B211">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>13274</v>
+        <v>14017</v>
       </c>
       <c r="B212">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C212">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>13276</v>
+        <v>14037</v>
       </c>
       <c r="B213">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C213">
-        <v>16</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>13280</v>
+        <v>19987</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>13403</v>
+        <v>20650</v>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C215">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>13467</v>
+        <v>21068</v>
       </c>
       <c r="B216">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C216">
-        <v>7</v>
+        <v>321</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>19987</v>
+        <v>21088</v>
       </c>
       <c r="B217">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C217">
-        <v>37</v>
+        <v>133</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>20208</v>
+        <v>21454</v>
       </c>
       <c r="B218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218">
         <v>7</v>
@@ -2783,288 +2783,189 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>20650</v>
+        <v>22317</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C219">
-        <v>7</v>
+        <v>189</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>21068</v>
+        <v>22631</v>
       </c>
       <c r="B220">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C220">
-        <v>309</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>21088</v>
+        <v>22665</v>
       </c>
       <c r="B221">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C221">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>21269</v>
+        <v>23235</v>
       </c>
       <c r="B222">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C222">
-        <v>397</v>
+        <v>50</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>21454</v>
+        <v>23335</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C223">
-        <v>21</v>
+        <v>225</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>22089</v>
+        <v>23336</v>
       </c>
       <c r="B224">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>22317</v>
+        <v>23491</v>
       </c>
       <c r="B225">
         <v>3</v>
       </c>
       <c r="C225">
-        <v>8</v>
+        <v>130</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>22631</v>
+        <v>23992</v>
       </c>
       <c r="B226">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C226">
-        <v>423</v>
+        <v>25</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>22665</v>
+        <v>24125</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C227">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>22667</v>
+        <v>24127</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C228">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>23234</v>
+        <v>24252</v>
       </c>
       <c r="B229">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>88</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>23238</v>
+        <v>24260</v>
       </c>
       <c r="B230">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C230">
-        <v>35</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>23335</v>
+        <v>25278</v>
       </c>
       <c r="B231">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C231">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>23380</v>
+        <v>25342</v>
       </c>
       <c r="B232">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C232">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>23961</v>
+        <v>25344</v>
       </c>
       <c r="B233">
         <v>3</v>
       </c>
       <c r="C233">
-        <v>417</v>
+        <v>98</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>23992</v>
+        <v>25345</v>
       </c>
       <c r="B234">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>24125</v>
+        <v>25899</v>
       </c>
       <c r="B235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C235">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236">
-        <v>24127</v>
-      </c>
-      <c r="B236">
-        <v>3</v>
-      </c>
-      <c r="C236">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237">
-        <v>24252</v>
-      </c>
-      <c r="B237">
-        <v>1</v>
-      </c>
-      <c r="C237">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238">
-        <v>24253</v>
-      </c>
-      <c r="B238">
-        <v>1</v>
-      </c>
-      <c r="C238">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239">
-        <v>24256</v>
-      </c>
-      <c r="B239">
-        <v>1</v>
-      </c>
-      <c r="C239">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240">
-        <v>24258</v>
-      </c>
-      <c r="B240">
-        <v>1</v>
-      </c>
-      <c r="C240">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241">
-        <v>25278</v>
-      </c>
-      <c r="B241">
-        <v>2</v>
-      </c>
-      <c r="C241">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242">
-        <v>25286</v>
-      </c>
-      <c r="B242">
-        <v>1</v>
-      </c>
-      <c r="C242">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>25342</v>
-      </c>
-      <c r="B243">
-        <v>3</v>
-      </c>
-      <c r="C243">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>25344</v>
-      </c>
-      <c r="B244">
-        <v>3</v>
-      </c>
-      <c r="C244">
-        <v>74</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C235"/>
+  <dimension ref="A1:C250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,51 +396,51 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -451,1066 +451,1066 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>69</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>69</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>725</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>136</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21">
-        <v>710</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>28</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>69</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>36</v>
+        <v>938</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>93</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>92</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>143</v>
+        <v>217</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>145</v>
+        <v>307</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>159</v>
+        <v>334</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>167</v>
+        <v>335</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32">
-        <v>135</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>168</v>
+        <v>336</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>482</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>170</v>
+        <v>344</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C34">
-        <v>216</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>192</v>
+        <v>414</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>913</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>201</v>
+        <v>416</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>391</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>211</v>
+        <v>418</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>38</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>214</v>
+        <v>515</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C38">
-        <v>397</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>220</v>
+        <v>523</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>31</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>248</v>
+        <v>563</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>308</v>
+        <v>590</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C41">
-        <v>202</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>335</v>
+        <v>616</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>773</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>336</v>
+        <v>624</v>
       </c>
       <c r="B43">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>361</v>
+        <v>641</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>362</v>
+        <v>823</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>112</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>409</v>
+        <v>858</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>410</v>
+        <v>922</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>413</v>
+        <v>926</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48">
-        <v>102</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>415</v>
+        <v>947</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C49">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>416</v>
+        <v>949</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C50">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>417</v>
+        <v>952</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>418</v>
+        <v>972</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>434</v>
+        <v>990</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>470</v>
+        <v>991</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>523</v>
+        <v>996</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>183</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>524</v>
+        <v>1006</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>66</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>590</v>
+        <v>1056</v>
       </c>
       <c r="B57">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>615</v>
+        <v>1070</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>616</v>
+        <v>1082</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>823</v>
+        <v>1309</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>944</v>
+        <v>1429</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>27</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>947</v>
+        <v>1448</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>949</v>
+        <v>1490</v>
       </c>
       <c r="B63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>950</v>
+        <v>1492</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>972</v>
+        <v>1519</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65">
-        <v>363</v>
+        <v>991</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>990</v>
+        <v>1599</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>991</v>
+        <v>1622</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1006</v>
+        <v>1656</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>136</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1056</v>
+        <v>1703</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1070</v>
+        <v>1801</v>
       </c>
       <c r="B70">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>451</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1080</v>
+        <v>2057</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="C71">
-        <v>83</v>
+        <v>285</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1082</v>
+        <v>2103</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C72">
-        <v>25</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1084</v>
+        <v>2108</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1087</v>
+        <v>2109</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1309</v>
+        <v>2328</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>34</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>1448</v>
+        <v>2335</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>24</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>1490</v>
+        <v>2422</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>30</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>1492</v>
+        <v>2537</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>1599</v>
+        <v>2726</v>
       </c>
       <c r="B79">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>1622</v>
+        <v>2728</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>125</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>1777</v>
+        <v>2729</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>66</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>1801</v>
+        <v>2735</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2049</v>
+        <v>2774</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>332</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2057</v>
+        <v>2878</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>285</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2104</v>
+        <v>2911</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>204</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2108</v>
+        <v>2912</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>159</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2109</v>
+        <v>3016</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C87">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2322</v>
+        <v>3049</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2328</v>
+        <v>3258</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>158</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2331</v>
+        <v>3429</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C90">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2335</v>
+        <v>3434</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>2537</v>
+        <v>3454</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>2774</v>
+        <v>3478</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>101</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>2878</v>
+        <v>3673</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>46</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>2911</v>
+        <v>3674</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>29</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>2912</v>
+        <v>3900</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>2935</v>
+        <v>4019</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>3454</v>
+        <v>4043</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>3478</v>
+        <v>4063</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>46</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>3674</v>
+        <v>4222</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C100">
-        <v>284</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>3889</v>
+        <v>4672</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>138</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>3900</v>
+        <v>4715</v>
       </c>
       <c r="B102">
         <v>3</v>
       </c>
       <c r="C102">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>3955</v>
+        <v>4728</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
         <v>7</v>
@@ -1518,54 +1518,54 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>4019</v>
+        <v>4867</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>4063</v>
+        <v>4882</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>332</v>
       </c>
       <c r="C105">
-        <v>318</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>4246</v>
+        <v>4901</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C106">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>4867</v>
+        <v>4960</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C107">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>4901</v>
+        <v>4967</v>
       </c>
       <c r="B108">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C108">
         <v>8</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5005</v>
+        <v>5121</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -1584,57 +1584,57 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>5081</v>
+        <v>5152</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>151</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5083</v>
+        <v>5153</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5152</v>
+        <v>5165</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5153</v>
+        <v>5341</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C113">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5165</v>
+        <v>5342</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C114">
-        <v>29</v>
+        <v>348</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="C116">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1689,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="C119">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -1705,120 +1705,120 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5584</v>
+        <v>5577</v>
       </c>
       <c r="B121">
         <v>3</v>
       </c>
       <c r="C121">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5644</v>
+        <v>5584</v>
       </c>
       <c r="B122">
         <v>3</v>
       </c>
       <c r="C122">
-        <v>21</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5723</v>
+        <v>5647</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>6097</v>
+        <v>5723</v>
       </c>
       <c r="B124">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>6097</v>
+        <v>5733</v>
       </c>
       <c r="B125">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>6098</v>
+        <v>6072</v>
       </c>
       <c r="B126">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="C126">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>6494</v>
+        <v>6097</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C127">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>6496</v>
+        <v>6097</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C128">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>6540</v>
+        <v>6098</v>
       </c>
       <c r="B129">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C129">
-        <v>92</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>6927</v>
+        <v>6494</v>
       </c>
       <c r="B130">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>6929</v>
+        <v>6497</v>
       </c>
       <c r="B131">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C131">
         <v>7</v>
@@ -1826,35 +1826,35 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>6936</v>
+        <v>6540</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>7004</v>
+        <v>6927</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C133">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>7005</v>
+        <v>6929</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1870,18 +1870,18 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>7084</v>
+        <v>7318</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C136">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>7318</v>
+        <v>7367</v>
       </c>
       <c r="B137">
         <v>12</v>
@@ -1898,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="C138">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1914,420 +1914,420 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>7885</v>
+        <v>7887</v>
       </c>
       <c r="B140">
         <v>4</v>
       </c>
       <c r="C140">
-        <v>85</v>
+        <v>168</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>7886</v>
+        <v>8055</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>86</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>7887</v>
+        <v>8104</v>
       </c>
       <c r="B142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>84</v>
+        <v>236</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8055</v>
+        <v>8106</v>
       </c>
       <c r="B143">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8104</v>
+        <v>8121</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>179</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>8106</v>
+        <v>8284</v>
       </c>
       <c r="B145">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>42</v>
+        <v>304</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8274</v>
+        <v>8286</v>
       </c>
       <c r="B146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>211</v>
+        <v>304</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8284</v>
+        <v>8677</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>294</v>
+        <v>364</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8286</v>
+        <v>8685</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C148">
-        <v>384</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8635</v>
+        <v>8688</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C149">
-        <v>204</v>
+        <v>227</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>8674</v>
+        <v>8753</v>
       </c>
       <c r="B150">
         <v>2</v>
       </c>
       <c r="C150">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8675</v>
+        <v>8926</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>172</v>
+        <v>37</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8677</v>
+        <v>8927</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C152">
-        <v>358</v>
+        <v>502</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8898</v>
+        <v>8945</v>
       </c>
       <c r="B153">
         <v>3</v>
       </c>
       <c r="C153">
-        <v>404</v>
+        <v>357</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>8915</v>
+        <v>8990</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C154">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>8926</v>
+        <v>9087</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C155">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>8939</v>
+        <v>9208</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C156">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>8945</v>
+        <v>9358</v>
       </c>
       <c r="B157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>355</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>8990</v>
+        <v>9785</v>
       </c>
       <c r="B158">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9081</v>
+        <v>9787</v>
       </c>
       <c r="B159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>581</v>
+        <v>58</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9087</v>
+        <v>9829</v>
       </c>
       <c r="B160">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C160">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9208</v>
+        <v>9833</v>
       </c>
       <c r="B161">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C161">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9760</v>
+        <v>9960</v>
       </c>
       <c r="B162">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9827</v>
+        <v>9997</v>
       </c>
       <c r="B163">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C163">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>9833</v>
+        <v>10105</v>
       </c>
       <c r="B164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C164">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>9960</v>
+        <v>10149</v>
       </c>
       <c r="B165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165">
-        <v>43</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>10105</v>
+        <v>10170</v>
       </c>
       <c r="B166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>10149</v>
+        <v>10185</v>
       </c>
       <c r="B167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C167">
-        <v>576</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>10170</v>
+        <v>10529</v>
       </c>
       <c r="B168">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C168">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>10529</v>
+        <v>10530</v>
       </c>
       <c r="B169">
         <v>29</v>
       </c>
       <c r="C169">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>10530</v>
+        <v>10616</v>
       </c>
       <c r="B170">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C170">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>10574</v>
+        <v>10716</v>
       </c>
       <c r="B171">
         <v>3</v>
       </c>
       <c r="C171">
-        <v>330</v>
+        <v>59</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>10616</v>
+        <v>10717</v>
       </c>
       <c r="B172">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C172">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>10716</v>
+        <v>10720</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C173">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>10717</v>
+        <v>10780</v>
       </c>
       <c r="B174">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C174">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>10720</v>
+        <v>10825</v>
       </c>
       <c r="B175">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C175">
-        <v>20</v>
+        <v>530</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>10825</v>
+        <v>10993</v>
       </c>
       <c r="B176">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C176">
-        <v>530</v>
+        <v>33</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>10993</v>
+        <v>11039</v>
       </c>
       <c r="B177">
         <v>2</v>
       </c>
       <c r="C177">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -2338,18 +2338,18 @@
         <v>3</v>
       </c>
       <c r="C178">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11116</v>
+        <v>11081</v>
       </c>
       <c r="B179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C179">
-        <v>47</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -2360,117 +2360,117 @@
         <v>1</v>
       </c>
       <c r="C180">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11403</v>
+        <v>11234</v>
       </c>
       <c r="B181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181">
-        <v>55</v>
+        <v>111</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11404</v>
+        <v>11396</v>
       </c>
       <c r="B182">
         <v>2</v>
       </c>
       <c r="C182">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11493</v>
+        <v>11399</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11555</v>
+        <v>11402</v>
       </c>
       <c r="B184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184">
-        <v>80</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11583</v>
+        <v>11403</v>
       </c>
       <c r="B185">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C185">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11687</v>
+        <v>11471</v>
       </c>
       <c r="B186">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C186">
-        <v>245</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11895</v>
+        <v>11493</v>
       </c>
       <c r="B187">
         <v>1</v>
       </c>
       <c r="C187">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11914</v>
+        <v>11510</v>
       </c>
       <c r="B188">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>64</v>
+        <v>363</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11952</v>
+        <v>11555</v>
       </c>
       <c r="B189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11961</v>
+        <v>11895</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -2481,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="C191">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -2519,381 +2519,381 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12621</v>
+        <v>12598</v>
       </c>
       <c r="B195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12661</v>
+        <v>12621</v>
       </c>
       <c r="B196">
         <v>1</v>
       </c>
       <c r="C196">
-        <v>47</v>
+        <v>138</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12764</v>
+        <v>12661</v>
       </c>
       <c r="B197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C197">
-        <v>451</v>
+        <v>47</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>12870</v>
+        <v>12764</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C198">
-        <v>84</v>
+        <v>454</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>12923</v>
+        <v>12870</v>
       </c>
       <c r="B199">
         <v>1</v>
       </c>
       <c r="C199">
-        <v>22</v>
+        <v>84</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>12924</v>
+        <v>12923</v>
       </c>
       <c r="B200">
         <v>1</v>
       </c>
       <c r="C200">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>12925</v>
+        <v>12924</v>
       </c>
       <c r="B201">
         <v>1</v>
       </c>
       <c r="C201">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>12930</v>
+        <v>12925</v>
       </c>
       <c r="B202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C202">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>13249</v>
+        <v>12930</v>
       </c>
       <c r="B203">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C203">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>13256</v>
+        <v>13028</v>
       </c>
       <c r="B204">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C204">
-        <v>52</v>
+        <v>176</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>13259</v>
+        <v>13249</v>
       </c>
       <c r="B205">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C205">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13260</v>
+        <v>13256</v>
       </c>
       <c r="B206">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C206">
-        <v>86</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13263</v>
+        <v>13259</v>
       </c>
       <c r="B207">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C207">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13264</v>
+        <v>13263</v>
       </c>
       <c r="B208">
         <v>29</v>
       </c>
       <c r="C208">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>13269</v>
+        <v>13264</v>
       </c>
       <c r="B209">
         <v>29</v>
       </c>
       <c r="C209">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>13280</v>
+        <v>13269</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C210">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>13403</v>
+        <v>13276</v>
       </c>
       <c r="B211">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C211">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>14017</v>
+        <v>13403</v>
       </c>
       <c r="B212">
         <v>3</v>
       </c>
       <c r="C212">
-        <v>121</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>14037</v>
+        <v>13467</v>
       </c>
       <c r="B213">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C213">
-        <v>204</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>19987</v>
+        <v>13968</v>
       </c>
       <c r="B214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>20650</v>
+        <v>14017</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>21068</v>
+        <v>14037</v>
       </c>
       <c r="B216">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>321</v>
+        <v>204</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>21088</v>
+        <v>18964</v>
       </c>
       <c r="B217">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C217">
-        <v>133</v>
+        <v>40</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>21454</v>
+        <v>19047</v>
       </c>
       <c r="B218">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>180</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>22317</v>
+        <v>19685</v>
       </c>
       <c r="B219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>189</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>22631</v>
+        <v>19987</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C220">
-        <v>460</v>
+        <v>39</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>22665</v>
+        <v>20208</v>
       </c>
       <c r="B221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C221">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>23235</v>
+        <v>20486</v>
       </c>
       <c r="B222">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C222">
-        <v>50</v>
+        <v>83</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>23335</v>
+        <v>20650</v>
       </c>
       <c r="B223">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C223">
-        <v>225</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>23336</v>
+        <v>20969</v>
       </c>
       <c r="B224">
         <v>3</v>
       </c>
       <c r="C224">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>23491</v>
+        <v>21068</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C225">
-        <v>130</v>
+        <v>324</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>23992</v>
+        <v>21088</v>
       </c>
       <c r="B226">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C226">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>24125</v>
+        <v>21454</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>24127</v>
+        <v>21793</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>7</v>
+        <v>288</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>24252</v>
+        <v>21798</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -2904,68 +2904,233 @@
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>24260</v>
+        <v>22089</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C230">
-        <v>168</v>
+        <v>124</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>25278</v>
+        <v>22313</v>
       </c>
       <c r="B231">
         <v>2</v>
       </c>
       <c r="C231">
-        <v>171</v>
+        <v>42</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>25342</v>
+        <v>22554</v>
       </c>
       <c r="B232">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C232">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>25344</v>
+        <v>22631</v>
       </c>
       <c r="B233">
         <v>3</v>
       </c>
       <c r="C233">
-        <v>98</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>25345</v>
+        <v>22665</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C234">
-        <v>77</v>
+        <v>17</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>25899</v>
+        <v>22667</v>
       </c>
       <c r="B235">
         <v>2</v>
       </c>
       <c r="C235">
-        <v>103</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <v>23336</v>
+      </c>
+      <c r="B236">
+        <v>3</v>
+      </c>
+      <c r="C236">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <v>23489</v>
+      </c>
+      <c r="B237">
+        <v>3</v>
+      </c>
+      <c r="C237">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <v>23491</v>
+      </c>
+      <c r="B238">
+        <v>3</v>
+      </c>
+      <c r="C238">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <v>23992</v>
+      </c>
+      <c r="B239">
+        <v>29</v>
+      </c>
+      <c r="C239">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>24125</v>
+      </c>
+      <c r="B240">
+        <v>3</v>
+      </c>
+      <c r="C240">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <v>24127</v>
+      </c>
+      <c r="B241">
+        <v>3</v>
+      </c>
+      <c r="C241">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <v>24252</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <v>24253</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <v>24260</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245">
+        <v>24705</v>
+      </c>
+      <c r="B245">
+        <v>2</v>
+      </c>
+      <c r="C245">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246">
+        <v>25278</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247">
+        <v>25286</v>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248">
+        <v>25342</v>
+      </c>
+      <c r="B248">
+        <v>3</v>
+      </c>
+      <c r="C248">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249">
+        <v>25344</v>
+      </c>
+      <c r="B249">
+        <v>3</v>
+      </c>
+      <c r="C249">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250">
+        <v>25345</v>
+      </c>
+      <c r="B250">
+        <v>3</v>
+      </c>
+      <c r="C250">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C250"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,73 +402,73 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>136</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -479,7 +479,7 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -495,546 +495,546 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>341</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>99</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>725</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>130</v>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>69</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>125</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>135</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>482</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C23">
-        <v>221</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>938</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25">
-        <v>391</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>128</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>308</v>
+        <v>214</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>202</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>334</v>
+        <v>215</v>
       </c>
       <c r="B31">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>335</v>
+        <v>248</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>781</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="B34">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>65</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>414</v>
+        <v>335</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>69</v>
+        <v>764</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>416</v>
+        <v>336</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C36">
-        <v>101</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>418</v>
+        <v>344</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C37">
-        <v>111</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>515</v>
+        <v>345</v>
       </c>
       <c r="B38">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>126</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>523</v>
+        <v>362</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>183</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>563</v>
+        <v>378</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
-        <v>44</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>590</v>
+        <v>409</v>
       </c>
       <c r="B41">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>616</v>
+        <v>410</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>624</v>
+        <v>411</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>641</v>
+        <v>413</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>823</v>
+        <v>414</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>858</v>
+        <v>416</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>30</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>922</v>
+        <v>418</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>29</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>926</v>
+        <v>515</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C48">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>947</v>
+        <v>590</v>
       </c>
       <c r="B49">
         <v>15</v>
       </c>
       <c r="C49">
-        <v>25</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>949</v>
+        <v>615</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>41</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>952</v>
+        <v>616</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>972</v>
+        <v>823</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>363</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>990</v>
+        <v>922</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>991</v>
+        <v>926</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>996</v>
+        <v>947</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1006</v>
+        <v>949</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>136</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1056</v>
+        <v>950</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1070</v>
+        <v>990</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>451</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1082</v>
+        <v>991</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1309</v>
+        <v>1082</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -1045,332 +1045,332 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1429</v>
+        <v>1120</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1448</v>
+        <v>1126</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>24</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1490</v>
+        <v>1243</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1492</v>
+        <v>1309</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1519</v>
+        <v>1413</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>991</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1599</v>
+        <v>1414</v>
       </c>
       <c r="B66">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1622</v>
+        <v>1448</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1656</v>
+        <v>1490</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1703</v>
+        <v>1519</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>193</v>
+        <v>990</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1801</v>
+        <v>1599</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2057</v>
+        <v>1622</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>285</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2103</v>
+        <v>1655</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>206</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2108</v>
+        <v>1656</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>159</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2109</v>
+        <v>1703</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>23</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2328</v>
+        <v>1801</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>158</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2335</v>
+        <v>2049</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76">
-        <v>123</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2422</v>
+        <v>2103</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C77">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2537</v>
+        <v>2104</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>23</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2726</v>
+        <v>2105</v>
       </c>
       <c r="B79">
         <v>3</v>
       </c>
       <c r="C79">
-        <v>74</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2728</v>
+        <v>2108</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80">
-        <v>62</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2729</v>
+        <v>2328</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2735</v>
+        <v>2331</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2774</v>
+        <v>2422</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C83">
-        <v>101</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2878</v>
+        <v>2423</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C84">
-        <v>46</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2911</v>
+        <v>2537</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2912</v>
+        <v>2774</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>29</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>3016</v>
+        <v>2878</v>
       </c>
       <c r="B87">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>3049</v>
+        <v>2912</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>3258</v>
+        <v>2935</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>3429</v>
+        <v>3258</v>
       </c>
       <c r="B90">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1397,139 +1397,139 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>3478</v>
+        <v>3462</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>3673</v>
+        <v>3478</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>155</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3674</v>
+        <v>3495</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>282</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3900</v>
+        <v>3671</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>4019</v>
+        <v>3673</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>4043</v>
+        <v>3674</v>
       </c>
       <c r="B98">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>22</v>
+        <v>285</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>4063</v>
+        <v>3891</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>419</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>4222</v>
+        <v>3893</v>
       </c>
       <c r="B100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>4672</v>
+        <v>4019</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>4715</v>
+        <v>4672</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>4728</v>
+        <v>4867</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>4867</v>
+        <v>4880</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C104">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>4882</v>
+        <v>4901</v>
       </c>
       <c r="B105">
         <v>332</v>
@@ -1540,46 +1540,46 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>4901</v>
+        <v>5005</v>
       </c>
       <c r="B106">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>4960</v>
+        <v>5081</v>
       </c>
       <c r="B107">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>26</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>4967</v>
+        <v>5086</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5121</v>
+        <v>5151</v>
       </c>
       <c r="B109">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1617,274 +1617,274 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5341</v>
+        <v>5209</v>
       </c>
       <c r="B113">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>340</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5342</v>
+        <v>5343</v>
       </c>
       <c r="B114">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C114">
-        <v>348</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5343</v>
+        <v>5435</v>
       </c>
       <c r="B115">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5435</v>
+        <v>5490</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>5490</v>
+        <v>5493</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5491</v>
+        <v>5494</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5493</v>
+        <v>5660</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5494</v>
+        <v>5723</v>
       </c>
       <c r="B120">
         <v>2</v>
       </c>
       <c r="C120">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5577</v>
+        <v>5733</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>132</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5584</v>
+        <v>5831</v>
       </c>
       <c r="B122">
         <v>3</v>
       </c>
       <c r="C122">
-        <v>158</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>5647</v>
+        <v>6097</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>5723</v>
+        <v>6097</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C124">
-        <v>36</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>5733</v>
+        <v>6098</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>6072</v>
+        <v>6158</v>
       </c>
       <c r="B126">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>20</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>6097</v>
+        <v>6494</v>
       </c>
       <c r="B127">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>6097</v>
+        <v>6496</v>
       </c>
       <c r="B128">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>6098</v>
+        <v>6540</v>
       </c>
       <c r="B129">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C129">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>6494</v>
+        <v>6927</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C130">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>6497</v>
+        <v>6928</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>6540</v>
+        <v>6929</v>
       </c>
       <c r="B132">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>6927</v>
+        <v>6935</v>
       </c>
       <c r="B133">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6929</v>
+        <v>6936</v>
       </c>
       <c r="B134">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>7036</v>
+        <v>7004</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>7318</v>
+        <v>7005</v>
       </c>
       <c r="B136">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>7367</v>
+        <v>7036</v>
       </c>
       <c r="B137">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -1892,189 +1892,189 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>7457</v>
+        <v>7318</v>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C138">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>7520</v>
+        <v>7457</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>12</v>
+        <v>134</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>7887</v>
+        <v>7520</v>
       </c>
       <c r="B140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>168</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>8055</v>
+        <v>7887</v>
       </c>
       <c r="B141">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>8104</v>
+        <v>8055</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C142">
-        <v>236</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8106</v>
+        <v>8104</v>
       </c>
       <c r="B143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>42</v>
+        <v>234</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8121</v>
+        <v>8106</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C144">
-        <v>179</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>8284</v>
+        <v>8121</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>304</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8286</v>
+        <v>8284</v>
       </c>
       <c r="B146">
         <v>2</v>
       </c>
       <c r="C146">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8677</v>
+        <v>8286</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>364</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8685</v>
+        <v>8635</v>
       </c>
       <c r="B148">
         <v>3</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>210</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8688</v>
+        <v>8915</v>
       </c>
       <c r="B149">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>227</v>
+        <v>96</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>8753</v>
+        <v>8927</v>
       </c>
       <c r="B150">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C150">
-        <v>218</v>
+        <v>977</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8926</v>
+        <v>8939</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>37</v>
+        <v>126</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8927</v>
+        <v>8945</v>
       </c>
       <c r="B152">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>502</v>
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8945</v>
+        <v>8990</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C153">
-        <v>357</v>
+        <v>65</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>8990</v>
+        <v>9081</v>
       </c>
       <c r="B154">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>65</v>
+        <v>579</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2085,7 +2085,7 @@
         <v>29</v>
       </c>
       <c r="C155">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2101,79 +2101,79 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>9358</v>
+        <v>9239</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C157">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9785</v>
+        <v>9289</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C158">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9787</v>
+        <v>9358</v>
       </c>
       <c r="B159">
         <v>1</v>
       </c>
       <c r="C159">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9829</v>
+        <v>9691</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C160">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9833</v>
+        <v>9760</v>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C161">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9960</v>
+        <v>9833</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162">
-        <v>43</v>
+        <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9997</v>
+        <v>9960</v>
       </c>
       <c r="B163">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C163">
-        <v>79</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -2195,7 +2195,7 @@
         <v>3</v>
       </c>
       <c r="C165">
-        <v>586</v>
+        <v>576</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2211,13 +2211,13 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>10185</v>
+        <v>10517</v>
       </c>
       <c r="B167">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C167">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2228,7 +2228,7 @@
         <v>29</v>
       </c>
       <c r="C168">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2239,7 +2239,7 @@
         <v>29</v>
       </c>
       <c r="C169">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -2250,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="C170">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -2261,7 +2261,7 @@
         <v>3</v>
       </c>
       <c r="C171">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -2272,7 +2272,7 @@
         <v>3</v>
       </c>
       <c r="C172">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -2288,178 +2288,178 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>10780</v>
+        <v>10825</v>
       </c>
       <c r="B174">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C174">
-        <v>7</v>
+        <v>804</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>10825</v>
+        <v>11059</v>
       </c>
       <c r="B175">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C175">
-        <v>530</v>
+        <v>24</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>10993</v>
+        <v>11081</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C176">
-        <v>33</v>
+        <v>220</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11039</v>
+        <v>11116</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11059</v>
+        <v>11150</v>
       </c>
       <c r="B178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11081</v>
+        <v>11396</v>
       </c>
       <c r="B179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C179">
-        <v>291</v>
+        <v>54</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11150</v>
+        <v>11399</v>
       </c>
       <c r="B180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C180">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11234</v>
+        <v>11402</v>
       </c>
       <c r="B181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181">
-        <v>111</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11396</v>
+        <v>11403</v>
       </c>
       <c r="B182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11399</v>
+        <v>11490</v>
       </c>
       <c r="B183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C183">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11402</v>
+        <v>11493</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11403</v>
+        <v>11555</v>
       </c>
       <c r="B185">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11471</v>
+        <v>11583</v>
       </c>
       <c r="B186">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C186">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11493</v>
+        <v>11681</v>
       </c>
       <c r="B187">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11510</v>
+        <v>11711</v>
       </c>
       <c r="B188">
         <v>3</v>
       </c>
       <c r="C188">
-        <v>363</v>
+        <v>164</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11555</v>
+        <v>11794</v>
       </c>
       <c r="B189">
         <v>2</v>
       </c>
       <c r="C189">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2519,362 +2519,362 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12598</v>
+        <v>12621</v>
       </c>
       <c r="B195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C195">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12621</v>
+        <v>12870</v>
       </c>
       <c r="B196">
         <v>1</v>
       </c>
       <c r="C196">
-        <v>138</v>
+        <v>84</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12661</v>
+        <v>12923</v>
       </c>
       <c r="B197">
         <v>1</v>
       </c>
       <c r="C197">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>12764</v>
+        <v>12924</v>
       </c>
       <c r="B198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198">
-        <v>454</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>12870</v>
+        <v>12925</v>
       </c>
       <c r="B199">
         <v>1</v>
       </c>
       <c r="C199">
-        <v>84</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>12923</v>
+        <v>12930</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C200">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>12924</v>
+        <v>13028</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C201">
-        <v>32</v>
+        <v>176</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>12925</v>
+        <v>13256</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C202">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>12930</v>
+        <v>13259</v>
       </c>
       <c r="B203">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C203">
-        <v>64</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>13028</v>
+        <v>13263</v>
       </c>
       <c r="B204">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C204">
-        <v>176</v>
+        <v>54</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>13249</v>
+        <v>13264</v>
       </c>
       <c r="B205">
         <v>29</v>
       </c>
       <c r="C205">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13256</v>
+        <v>13272</v>
       </c>
       <c r="B206">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C206">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13259</v>
+        <v>13276</v>
       </c>
       <c r="B207">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C207">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13263</v>
+        <v>13403</v>
       </c>
       <c r="B208">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C208">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>13264</v>
+        <v>19685</v>
       </c>
       <c r="B209">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C209">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>13269</v>
+        <v>19987</v>
       </c>
       <c r="B210">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C210">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>13276</v>
+        <v>20208</v>
       </c>
       <c r="B211">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>13403</v>
+        <v>20486</v>
       </c>
       <c r="B212">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C212">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>13467</v>
+        <v>20650</v>
       </c>
       <c r="B213">
         <v>1</v>
       </c>
       <c r="C213">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>13968</v>
+        <v>20927</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>14017</v>
+        <v>21068</v>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C215">
-        <v>121</v>
+        <v>314</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>14037</v>
+        <v>21088</v>
       </c>
       <c r="B216">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C216">
-        <v>204</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>18964</v>
+        <v>21454</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>19047</v>
+        <v>22317</v>
       </c>
       <c r="B218">
         <v>3</v>
       </c>
       <c r="C218">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>19685</v>
+        <v>22554</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C219">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>19987</v>
+        <v>22565</v>
       </c>
       <c r="B220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C220">
-        <v>39</v>
+        <v>710</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>20208</v>
+        <v>22631</v>
       </c>
       <c r="B221">
         <v>3</v>
       </c>
       <c r="C221">
-        <v>23</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>20486</v>
+        <v>22665</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C222">
-        <v>83</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>20650</v>
+        <v>23335</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C223">
-        <v>7</v>
+        <v>227</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>20969</v>
+        <v>23336</v>
       </c>
       <c r="B224">
         <v>3</v>
       </c>
       <c r="C224">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>21068</v>
+        <v>23994</v>
       </c>
       <c r="B225">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C225">
-        <v>324</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>21088</v>
+        <v>24125</v>
       </c>
       <c r="B226">
+        <v>3</v>
+      </c>
+      <c r="C226">
         <v>7</v>
-      </c>
-      <c r="C226">
-        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>21454</v>
+        <v>24252</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C227">
         <v>7</v>
@@ -2882,255 +2882,90 @@
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>21793</v>
+        <v>24260</v>
       </c>
       <c r="B228">
         <v>1</v>
       </c>
       <c r="C228">
-        <v>288</v>
+        <v>85</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>21798</v>
+        <v>24669</v>
       </c>
       <c r="B229">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>22089</v>
+        <v>25278</v>
       </c>
       <c r="B230">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C230">
-        <v>124</v>
+        <v>171</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>22313</v>
+        <v>25286</v>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>22554</v>
+        <v>25342</v>
       </c>
       <c r="B232">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C232">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>22631</v>
+        <v>25344</v>
       </c>
       <c r="B233">
         <v>3</v>
       </c>
       <c r="C233">
-        <v>463</v>
+        <v>98</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>22665</v>
+        <v>25345</v>
       </c>
       <c r="B234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>22667</v>
+        <v>25899</v>
       </c>
       <c r="B235">
         <v>2</v>
       </c>
       <c r="C235">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236">
-        <v>23336</v>
-      </c>
-      <c r="B236">
-        <v>3</v>
-      </c>
-      <c r="C236">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237">
-        <v>23489</v>
-      </c>
-      <c r="B237">
-        <v>3</v>
-      </c>
-      <c r="C237">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238">
-        <v>23491</v>
-      </c>
-      <c r="B238">
-        <v>3</v>
-      </c>
-      <c r="C238">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239">
-        <v>23992</v>
-      </c>
-      <c r="B239">
-        <v>29</v>
-      </c>
-      <c r="C239">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240">
-        <v>24125</v>
-      </c>
-      <c r="B240">
-        <v>3</v>
-      </c>
-      <c r="C240">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241">
-        <v>24127</v>
-      </c>
-      <c r="B241">
-        <v>3</v>
-      </c>
-      <c r="C241">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242">
-        <v>24252</v>
-      </c>
-      <c r="B242">
-        <v>1</v>
-      </c>
-      <c r="C242">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>24253</v>
-      </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>24260</v>
-      </c>
-      <c r="B244">
-        <v>1</v>
-      </c>
-      <c r="C244">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>24705</v>
-      </c>
-      <c r="B245">
-        <v>2</v>
-      </c>
-      <c r="C245">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>25278</v>
-      </c>
-      <c r="B246">
-        <v>2</v>
-      </c>
-      <c r="C246">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>25286</v>
-      </c>
-      <c r="B247">
-        <v>1</v>
-      </c>
-      <c r="C247">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248">
-        <v>25342</v>
-      </c>
-      <c r="B248">
-        <v>3</v>
-      </c>
-      <c r="C248">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249">
-        <v>25344</v>
-      </c>
-      <c r="B249">
-        <v>3</v>
-      </c>
-      <c r="C249">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250">
-        <v>25345</v>
-      </c>
-      <c r="B250">
-        <v>3</v>
-      </c>
-      <c r="C250">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C235"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,1242 +396,1242 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>68</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>68</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>73</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>29</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>457</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>146</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>725</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>130</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>69</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>35</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>124</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>145</v>
+        <v>305</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="B23">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>147</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>159</v>
+        <v>361</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>168</v>
+        <v>362</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>482</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>170</v>
+        <v>411</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>222</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>201</v>
+        <v>412</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>391</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>206</v>
+        <v>414</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>214</v>
+        <v>415</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>402</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>215</v>
+        <v>416</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>24</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>248</v>
+        <v>417</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>307</v>
+        <v>466</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>89</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>308</v>
+        <v>475</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>335</v>
+        <v>491</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>764</v>
+        <v>525</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>336</v>
+        <v>523</v>
       </c>
       <c r="B36">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>344</v>
+        <v>524</v>
       </c>
       <c r="B37">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>345</v>
+        <v>589</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>195</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>362</v>
+        <v>590</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>378</v>
+        <v>922</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>220</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>409</v>
+        <v>924</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>410</v>
+        <v>925</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>411</v>
+        <v>926</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>85</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>413</v>
+        <v>944</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>414</v>
+        <v>950</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>416</v>
+        <v>952</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>418</v>
+        <v>1070</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>111</v>
+        <v>679</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>515</v>
+        <v>1082</v>
       </c>
       <c r="B48">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>130</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>590</v>
+        <v>1087</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>615</v>
+        <v>1091</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>616</v>
+        <v>1124</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>61</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>823</v>
+        <v>1309</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>922</v>
+        <v>1429</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>29</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>926</v>
+        <v>1447</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>947</v>
+        <v>1448</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>949</v>
+        <v>1599</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C56">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>950</v>
+        <v>1622</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57">
-        <v>35</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>990</v>
+        <v>1656</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>991</v>
+        <v>1703</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>32</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1082</v>
+        <v>1705</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C60">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1120</v>
+        <v>1776</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1126</v>
+        <v>1777</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>275</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1243</v>
+        <v>1895</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>60</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1309</v>
+        <v>2105</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>33</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1413</v>
+        <v>2109</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>62</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1414</v>
+        <v>2188</v>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1448</v>
+        <v>2328</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1490</v>
+        <v>2331</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1519</v>
+        <v>2335</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69">
-        <v>990</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1599</v>
+        <v>2422</v>
       </c>
       <c r="B70">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1622</v>
+        <v>2423</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1655</v>
+        <v>2424</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C72">
-        <v>55</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1656</v>
+        <v>2436</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1703</v>
+        <v>2438</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>193</v>
+        <v>764</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1801</v>
+        <v>2703</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>62</v>
+        <v>176</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2049</v>
+        <v>2729</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76">
-        <v>332</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2103</v>
+        <v>2854</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C77">
-        <v>209</v>
+        <v>676</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2104</v>
+        <v>2859</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C78">
-        <v>203</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2105</v>
+        <v>2878</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>178</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2108</v>
+        <v>2911</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>161</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2328</v>
+        <v>2912</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2331</v>
+        <v>2916</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2422</v>
+        <v>2991</v>
       </c>
       <c r="B83">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>225</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2423</v>
+        <v>3016</v>
       </c>
       <c r="B84">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C84">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2537</v>
+        <v>3257</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C85">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2774</v>
+        <v>3429</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C86">
-        <v>198</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2878</v>
+        <v>3454</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2912</v>
+        <v>3495</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>29</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2935</v>
+        <v>4718</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>3258</v>
+        <v>4867</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>3434</v>
+        <v>4901</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C91">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>3454</v>
+        <v>4959</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>3462</v>
+        <v>4967</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>3478</v>
+        <v>5152</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>46</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3495</v>
+        <v>5342</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C95">
-        <v>1172</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3671</v>
+        <v>5343</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3673</v>
+        <v>5434</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>3674</v>
+        <v>5446</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C98">
-        <v>285</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>3891</v>
+        <v>5490</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>3893</v>
+        <v>5491</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>4019</v>
+        <v>5493</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>4672</v>
+        <v>5494</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>4867</v>
+        <v>5577</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>4880</v>
+        <v>5652</v>
       </c>
       <c r="B104">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>4901</v>
+        <v>5654</v>
       </c>
       <c r="B105">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>5005</v>
+        <v>5656</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>5081</v>
+        <v>5723</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>151</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>5086</v>
+        <v>5729</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>212</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5151</v>
+        <v>5733</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>5152</v>
+        <v>6072</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5153</v>
+        <v>6097</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C111">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5165</v>
+        <v>6097</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C112">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5209</v>
+        <v>6098</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C113">
-        <v>340</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5343</v>
+        <v>7036</v>
       </c>
       <c r="B114">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -1639,252 +1639,252 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5435</v>
+        <v>7367</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C115">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5490</v>
+        <v>7520</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>5493</v>
+        <v>7558</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5494</v>
+        <v>7885</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C118">
-        <v>62</v>
+        <v>85</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5660</v>
+        <v>7887</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C119">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5723</v>
+        <v>8055</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C120">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5733</v>
+        <v>8104</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>5831</v>
+        <v>8283</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>6097</v>
+        <v>8284</v>
       </c>
       <c r="B123">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>41</v>
+        <v>303</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>6097</v>
+        <v>8285</v>
       </c>
       <c r="B124">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>83</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>6098</v>
+        <v>8286</v>
       </c>
       <c r="B125">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>23</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>6158</v>
+        <v>8648</v>
       </c>
       <c r="B126">
         <v>2</v>
       </c>
       <c r="C126">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>6494</v>
+        <v>8674</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
-        <v>31</v>
+        <v>334</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>6496</v>
+        <v>8688</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C128">
-        <v>24</v>
+        <v>230</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>6540</v>
+        <v>8915</v>
       </c>
       <c r="B129">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>6927</v>
+        <v>8939</v>
       </c>
       <c r="B130">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>6928</v>
+        <v>8943</v>
       </c>
       <c r="B131">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>231</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>6929</v>
+        <v>8990</v>
       </c>
       <c r="B132">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>6935</v>
+        <v>9065</v>
       </c>
       <c r="B133">
         <v>2</v>
       </c>
       <c r="C133">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>6936</v>
+        <v>9069</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>165</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>7004</v>
+        <v>9081</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>48</v>
+        <v>579</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>7005</v>
+        <v>9082</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>48</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>7036</v>
+        <v>9208</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -1892,849 +1892,849 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>7318</v>
+        <v>9289</v>
       </c>
       <c r="B138">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>7457</v>
+        <v>9827</v>
       </c>
       <c r="B139">
         <v>3</v>
       </c>
       <c r="C139">
-        <v>134</v>
+        <v>109</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>7520</v>
+        <v>9829</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>7887</v>
+        <v>9833</v>
       </c>
       <c r="B141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>8055</v>
+        <v>9960</v>
       </c>
       <c r="B142">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8104</v>
+        <v>10093</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>234</v>
+        <v>679</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8106</v>
+        <v>10105</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>8121</v>
+        <v>10149</v>
       </c>
       <c r="B145">
         <v>3</v>
       </c>
       <c r="C145">
-        <v>179</v>
+        <v>572</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8284</v>
+        <v>10170</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>303</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8286</v>
+        <v>10172</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>303</v>
+        <v>99</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8635</v>
+        <v>10185</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>210</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>8915</v>
+        <v>10465</v>
       </c>
       <c r="B149">
         <v>2</v>
       </c>
       <c r="C149">
-        <v>96</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>8927</v>
+        <v>10529</v>
       </c>
       <c r="B150">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C150">
-        <v>977</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>8939</v>
+        <v>10780</v>
       </c>
       <c r="B151">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>126</v>
+        <v>231</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>8945</v>
+        <v>10816</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152">
-        <v>357</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>8990</v>
+        <v>10825</v>
       </c>
       <c r="B153">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C153">
-        <v>65</v>
+        <v>411</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>9081</v>
+        <v>10993</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>579</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>9087</v>
+        <v>11044</v>
       </c>
       <c r="B155">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>9208</v>
+        <v>11046</v>
       </c>
       <c r="B156">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>9239</v>
+        <v>11084</v>
       </c>
       <c r="B157">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C157">
-        <v>17</v>
+        <v>333</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9289</v>
+        <v>11085</v>
       </c>
       <c r="B158">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C158">
-        <v>77</v>
+        <v>332</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9358</v>
+        <v>11087</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159">
-        <v>34</v>
+        <v>332</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9691</v>
+        <v>11490</v>
       </c>
       <c r="B160">
         <v>1</v>
       </c>
       <c r="C160">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9760</v>
+        <v>11491</v>
       </c>
       <c r="B161">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C161">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>9833</v>
+        <v>11492</v>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>77</v>
+        <v>56</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>9960</v>
+        <v>11493</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>10105</v>
+        <v>11611</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164">
-        <v>7</v>
+        <v>274</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>10149</v>
+        <v>11689</v>
       </c>
       <c r="B165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C165">
-        <v>576</v>
+        <v>191</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>10170</v>
+        <v>11717</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C166">
-        <v>34</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>10517</v>
+        <v>11868</v>
       </c>
       <c r="B167">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C167">
-        <v>85</v>
+        <v>176</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>10529</v>
+        <v>11886</v>
       </c>
       <c r="B168">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C168">
-        <v>33</v>
+        <v>117</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>10530</v>
+        <v>11895</v>
       </c>
       <c r="B169">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C169">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>10616</v>
+        <v>11914</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>10716</v>
+        <v>11962</v>
       </c>
       <c r="B171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C171">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>10717</v>
+        <v>11967</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C172">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>10720</v>
+        <v>11969</v>
       </c>
       <c r="B173">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>10825</v>
+        <v>11971</v>
       </c>
       <c r="B174">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>804</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>11059</v>
+        <v>12059</v>
       </c>
       <c r="B175">
         <v>3</v>
       </c>
       <c r="C175">
-        <v>24</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>11081</v>
+        <v>12128</v>
       </c>
       <c r="B176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>220</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11116</v>
+        <v>12139</v>
       </c>
       <c r="B177">
         <v>1</v>
       </c>
       <c r="C177">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11150</v>
+        <v>12141</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11396</v>
+        <v>12147</v>
       </c>
       <c r="B179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C179">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11399</v>
+        <v>12270</v>
       </c>
       <c r="B180">
         <v>2</v>
       </c>
       <c r="C180">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11402</v>
+        <v>12304</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11403</v>
+        <v>12535</v>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11490</v>
+        <v>12539</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183">
-        <v>64</v>
+        <v>18</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>11493</v>
+        <v>12596</v>
       </c>
       <c r="B184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>11555</v>
+        <v>12616</v>
       </c>
       <c r="B185">
         <v>2</v>
       </c>
       <c r="C185">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>11583</v>
+        <v>12621</v>
       </c>
       <c r="B186">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C186">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>11681</v>
+        <v>12764</v>
       </c>
       <c r="B187">
         <v>2</v>
       </c>
       <c r="C187">
-        <v>11</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>11711</v>
+        <v>12870</v>
       </c>
       <c r="B188">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C188">
-        <v>164</v>
+        <v>112</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>11794</v>
+        <v>12907</v>
       </c>
       <c r="B189">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C189">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>11895</v>
+        <v>12923</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>12128</v>
+        <v>13028</v>
       </c>
       <c r="B191">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C191">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>12535</v>
+        <v>13034</v>
       </c>
       <c r="B192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C192">
-        <v>35</v>
+        <v>728</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>12539</v>
+        <v>13249</v>
       </c>
       <c r="B193">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C193">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>12543</v>
+        <v>13258</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C194">
-        <v>7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12621</v>
+        <v>13266</v>
       </c>
       <c r="B195">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C195">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12870</v>
+        <v>13269</v>
       </c>
       <c r="B196">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C196">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12923</v>
+        <v>13283</v>
       </c>
       <c r="B197">
         <v>1</v>
       </c>
       <c r="C197">
-        <v>22</v>
+        <v>189</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>12924</v>
+        <v>13403</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C198">
-        <v>32</v>
+        <v>91</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>12925</v>
+        <v>13417</v>
       </c>
       <c r="B199">
         <v>1</v>
       </c>
       <c r="C199">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>12930</v>
+        <v>14037</v>
       </c>
       <c r="B200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C200">
-        <v>65</v>
+        <v>207</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>13028</v>
+        <v>19685</v>
       </c>
       <c r="B201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>176</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>13256</v>
+        <v>19924</v>
       </c>
       <c r="B202">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C202">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>13259</v>
+        <v>19971</v>
       </c>
       <c r="B203">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C203">
-        <v>21</v>
+        <v>229</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>13263</v>
+        <v>19981</v>
       </c>
       <c r="B204">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C204">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>13264</v>
+        <v>19982</v>
       </c>
       <c r="B205">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C205">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>13272</v>
+        <v>19987</v>
       </c>
       <c r="B206">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C206">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>13276</v>
+        <v>19988</v>
       </c>
       <c r="B207">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C207">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>13403</v>
+        <v>20486</v>
       </c>
       <c r="B208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C208">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>19685</v>
+        <v>20498</v>
       </c>
       <c r="B209">
         <v>1</v>
       </c>
       <c r="C209">
-        <v>21</v>
+        <v>117</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>19987</v>
+        <v>20555</v>
       </c>
       <c r="B210">
         <v>2</v>
       </c>
       <c r="C210">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>20208</v>
+        <v>20556</v>
       </c>
       <c r="B211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>20486</v>
+        <v>20650</v>
       </c>
       <c r="B212">
         <v>1</v>
       </c>
       <c r="C212">
-        <v>83</v>
+        <v>141</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>20650</v>
+        <v>20927</v>
       </c>
       <c r="B213">
         <v>1</v>
       </c>
       <c r="C213">
-        <v>100</v>
+        <v>48</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>20927</v>
+        <v>20984</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -2756,7 +2756,7 @@
         <v>7</v>
       </c>
       <c r="C216">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -2767,205 +2767,337 @@
         <v>2</v>
       </c>
       <c r="C217">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>22317</v>
+        <v>21793</v>
       </c>
       <c r="B218">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C218">
-        <v>191</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>22554</v>
+        <v>21946</v>
       </c>
       <c r="B219">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>22565</v>
+        <v>22313</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C220">
-        <v>710</v>
+        <v>41</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>22631</v>
+        <v>22554</v>
       </c>
       <c r="B221">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C221">
-        <v>466</v>
+        <v>436</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>22665</v>
+        <v>22565</v>
       </c>
       <c r="B222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>17</v>
+        <v>699</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>23335</v>
+        <v>22573</v>
       </c>
       <c r="B223">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>227</v>
+        <v>47</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>23336</v>
+        <v>22631</v>
       </c>
       <c r="B224">
         <v>3</v>
       </c>
       <c r="C224">
-        <v>21</v>
+        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>23994</v>
+        <v>22665</v>
       </c>
       <c r="B225">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C225">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>24125</v>
+        <v>23489</v>
       </c>
       <c r="B226">
         <v>3</v>
       </c>
       <c r="C226">
-        <v>7</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>24252</v>
+        <v>23491</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C227">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>24260</v>
+        <v>23492</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C228">
-        <v>85</v>
+        <v>129</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>24669</v>
+        <v>23493</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C229">
-        <v>18</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>25278</v>
+        <v>23494</v>
       </c>
       <c r="B230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C230">
-        <v>171</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>25286</v>
+        <v>23526</v>
       </c>
       <c r="B231">
         <v>1</v>
       </c>
       <c r="C231">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>25342</v>
+        <v>23611</v>
       </c>
       <c r="B232">
         <v>3</v>
       </c>
       <c r="C232">
-        <v>7</v>
+        <v>405</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>25344</v>
+        <v>23992</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C233">
-        <v>98</v>
+        <v>50</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>25345</v>
+        <v>23994</v>
       </c>
       <c r="B234">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C234">
-        <v>79</v>
+        <v>45</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>25899</v>
+        <v>24125</v>
       </c>
       <c r="B235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C235">
-        <v>103</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <v>24252</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <v>24253</v>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <v>24256</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <v>24260</v>
+      </c>
+      <c r="B239">
+        <v>1</v>
+      </c>
+      <c r="C239">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>24567</v>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <v>24705</v>
+      </c>
+      <c r="B241">
+        <v>2</v>
+      </c>
+      <c r="C241">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <v>25254</v>
+      </c>
+      <c r="B242">
+        <v>3</v>
+      </c>
+      <c r="C242">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <v>25286</v>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <v>25342</v>
+      </c>
+      <c r="B244">
+        <v>3</v>
+      </c>
+      <c r="C244">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245">
+        <v>25344</v>
+      </c>
+      <c r="B245">
+        <v>3</v>
+      </c>
+      <c r="C245">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246">
+        <v>26103</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247">
+        <v>26229</v>
+      </c>
+      <c r="B247">
+        <v>3</v>
+      </c>
+      <c r="C247">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,1165 +396,1165 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>174</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>120</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>451</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>99</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>513</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>160</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>93</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>124</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>135</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>305</v>
+        <v>142</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>308</v>
+        <v>143</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>101</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>361</v>
+        <v>145</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>92</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>362</v>
+        <v>151</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>411</v>
+        <v>152</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>97</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>51</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>414</v>
+        <v>167</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>415</v>
+        <v>168</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>51</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>416</v>
+        <v>170</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>168</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>417</v>
+        <v>192</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>901</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>466</v>
+        <v>201</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>475</v>
+        <v>205</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>491</v>
+        <v>305</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>525</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>523</v>
+        <v>308</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>524</v>
+        <v>336</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>589</v>
+        <v>345</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>80</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>590</v>
+        <v>346</v>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>922</v>
+        <v>361</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>924</v>
+        <v>378</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>29</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>925</v>
+        <v>413</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>926</v>
+        <v>415</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>944</v>
+        <v>417</v>
       </c>
       <c r="B44">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>950</v>
+        <v>440</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>952</v>
+        <v>466</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>1070</v>
+        <v>475</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>679</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>1082</v>
+        <v>590</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>25</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>1087</v>
+        <v>593</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>83</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>1091</v>
+        <v>615</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>1124</v>
+        <v>624</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>1309</v>
+        <v>823</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>1429</v>
+        <v>903</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>159</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>1447</v>
+        <v>922</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1448</v>
+        <v>925</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1599</v>
+        <v>926</v>
       </c>
       <c r="B56">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>79</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1622</v>
+        <v>944</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1656</v>
+        <v>947</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1703</v>
+        <v>955</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>196</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1705</v>
+        <v>965</v>
       </c>
       <c r="B60">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C60">
-        <v>44</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1776</v>
+        <v>974</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1777</v>
+        <v>990</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1895</v>
+        <v>998</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>240</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2105</v>
+        <v>1080</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2109</v>
+        <v>1087</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2188</v>
+        <v>1091</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2328</v>
+        <v>1124</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2331</v>
+        <v>1163</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>75</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2335</v>
+        <v>1309</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>236</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2422</v>
+        <v>1309</v>
       </c>
       <c r="B70">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>149</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2423</v>
+        <v>1407</v>
       </c>
       <c r="B71">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C71">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2424</v>
+        <v>1414</v>
       </c>
       <c r="B72">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C72">
-        <v>308</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2436</v>
+        <v>1447</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2438</v>
+        <v>1448</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>764</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2703</v>
+        <v>1599</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C75">
-        <v>176</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2729</v>
+        <v>1622</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>69</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2854</v>
+        <v>2049</v>
       </c>
       <c r="B77">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>676</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2859</v>
+        <v>2109</v>
       </c>
       <c r="B78">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2878</v>
+        <v>2328</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2911</v>
+        <v>2335</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>29</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2912</v>
+        <v>2423</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C81">
-        <v>29</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2916</v>
+        <v>2424</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>19</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2991</v>
+        <v>2436</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>3016</v>
+        <v>2438</v>
       </c>
       <c r="B84">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>30</v>
+        <v>501</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>3257</v>
+        <v>2878</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>95</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>3429</v>
+        <v>2879</v>
       </c>
       <c r="B86">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>3454</v>
+        <v>2911</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>3495</v>
+        <v>2912</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>1172</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>4718</v>
+        <v>2916</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>4867</v>
+        <v>2934</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>4901</v>
+        <v>2991</v>
       </c>
       <c r="B91">
-        <v>332</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>8</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>4959</v>
+        <v>3257</v>
       </c>
       <c r="B92">
-        <v>332</v>
+        <v>4</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>4967</v>
+        <v>3430</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>5152</v>
+        <v>3454</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>5342</v>
+        <v>3478</v>
       </c>
       <c r="B95">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>5343</v>
+        <v>3495</v>
       </c>
       <c r="B96">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>5434</v>
+        <v>3898</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>5446</v>
+        <v>4246</v>
       </c>
       <c r="B98">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>5490</v>
+        <v>4867</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>5491</v>
+        <v>4901</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>5493</v>
+        <v>4967</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>79</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>5494</v>
+        <v>5083</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>5577</v>
+        <v>5085</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>132</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>5652</v>
+        <v>5152</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>5654</v>
+        <v>5165</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>5656</v>
+        <v>5208</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>34</v>
+        <v>339</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>5723</v>
+        <v>5343</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C107">
         <v>7</v>
@@ -1562,535 +1562,535 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>5729</v>
+        <v>5453</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5733</v>
+        <v>5490</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>6072</v>
+        <v>5494</v>
       </c>
       <c r="B110">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>6097</v>
+        <v>5577</v>
       </c>
       <c r="B111">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>21</v>
+        <v>132</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>6097</v>
+        <v>5584</v>
       </c>
       <c r="B112">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>41</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>6098</v>
+        <v>5646</v>
       </c>
       <c r="B113">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>7036</v>
+        <v>5647</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>7367</v>
+        <v>5650</v>
       </c>
       <c r="B115">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>7520</v>
+        <v>5652</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>7558</v>
+        <v>5654</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>7885</v>
+        <v>5656</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>85</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>7887</v>
+        <v>5660</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>84</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>8055</v>
+        <v>5723</v>
       </c>
       <c r="B120">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>8104</v>
+        <v>5729</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>8283</v>
+        <v>6097</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C122">
-        <v>303</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>8284</v>
+        <v>6097</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C123">
-        <v>303</v>
+        <v>83</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>8285</v>
+        <v>6098</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>303</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>8286</v>
+        <v>6540</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C125">
-        <v>303</v>
+        <v>92</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>8648</v>
+        <v>6952</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>8674</v>
+        <v>7004</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>334</v>
+        <v>48</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>8688</v>
+        <v>7005</v>
       </c>
       <c r="B128">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>230</v>
+        <v>48</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>8915</v>
+        <v>7084</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>10</v>
+        <v>103</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>8939</v>
+        <v>7457</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>8943</v>
+        <v>7520</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>231</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>8990</v>
+        <v>7558</v>
       </c>
       <c r="B132">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>9065</v>
+        <v>7567</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>191</v>
+        <v>43</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>9069</v>
+        <v>8055</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C134">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>9081</v>
+        <v>8104</v>
       </c>
       <c r="B135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>579</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>9082</v>
+        <v>8157</v>
       </c>
       <c r="B136">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>2991</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>9208</v>
+        <v>8216</v>
       </c>
       <c r="B137">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>9289</v>
+        <v>8274</v>
       </c>
       <c r="B138">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>52</v>
+        <v>208</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>9827</v>
+        <v>8283</v>
       </c>
       <c r="B139">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>109</v>
+        <v>303</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>9829</v>
+        <v>8284</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>303</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>9833</v>
+        <v>8285</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>76</v>
+        <v>303</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>9960</v>
+        <v>8286</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>22</v>
+        <v>303</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>10093</v>
+        <v>8672</v>
       </c>
       <c r="B143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143">
-        <v>679</v>
+        <v>169</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>10105</v>
+        <v>8674</v>
       </c>
       <c r="B144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>225</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>10149</v>
+        <v>8676</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C145">
-        <v>572</v>
+        <v>169</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>10170</v>
+        <v>8853</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>33</v>
+        <v>325</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>10172</v>
+        <v>8945</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>99</v>
+        <v>468</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>10185</v>
+        <v>8990</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C148">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>10465</v>
+        <v>9065</v>
       </c>
       <c r="B149">
         <v>2</v>
       </c>
       <c r="C149">
-        <v>8</v>
+        <v>191</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>10529</v>
+        <v>9068</v>
       </c>
       <c r="B150">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>10780</v>
+        <v>9069</v>
       </c>
       <c r="B151">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>231</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>10816</v>
+        <v>9070</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C152">
-        <v>399</v>
+        <v>39</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>10825</v>
+        <v>9081</v>
       </c>
       <c r="B153">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>411</v>
+        <v>583</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>10993</v>
+        <v>9087</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C154">
-        <v>33</v>
+        <v>87</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>11044</v>
+        <v>9289</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C155">
-        <v>28</v>
+        <v>115</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>11046</v>
+        <v>9357</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2101,706 +2101,706 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>11084</v>
+        <v>9608</v>
       </c>
       <c r="B157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>333</v>
+        <v>38</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>11085</v>
+        <v>9613</v>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>332</v>
+        <v>50</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>11087</v>
+        <v>9829</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>332</v>
+        <v>85</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>11490</v>
+        <v>9833</v>
       </c>
       <c r="B160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>11491</v>
+        <v>9960</v>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>11492</v>
+        <v>10170</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>11493</v>
+        <v>10524</v>
       </c>
       <c r="B163">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C163">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>11611</v>
+        <v>10529</v>
       </c>
       <c r="B164">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C164">
-        <v>274</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>11689</v>
+        <v>10530</v>
       </c>
       <c r="B165">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C165">
-        <v>191</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>11717</v>
+        <v>10719</v>
       </c>
       <c r="B166">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C166">
-        <v>374</v>
+        <v>120</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>11868</v>
+        <v>10816</v>
       </c>
       <c r="B167">
         <v>3</v>
       </c>
       <c r="C167">
-        <v>176</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>11886</v>
+        <v>10825</v>
       </c>
       <c r="B168">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C168">
-        <v>117</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>11895</v>
+        <v>11116</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>11914</v>
+        <v>11150</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>95</v>
+        <v>27</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>11962</v>
+        <v>11492</v>
       </c>
       <c r="B171">
         <v>1</v>
       </c>
       <c r="C171">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>11967</v>
+        <v>11493</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>81</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>11969</v>
+        <v>11687</v>
       </c>
       <c r="B173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C173">
-        <v>45</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>11971</v>
+        <v>11689</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174">
-        <v>24</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>12059</v>
+        <v>11711</v>
       </c>
       <c r="B175">
         <v>3</v>
       </c>
       <c r="C175">
-        <v>173</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>12128</v>
+        <v>11738</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>12139</v>
+        <v>11739</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C177">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>12141</v>
+        <v>11794</v>
       </c>
       <c r="B178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>12147</v>
+        <v>11848</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>12270</v>
+        <v>11895</v>
       </c>
       <c r="B180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C180">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>12304</v>
+        <v>11962</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>12535</v>
+        <v>11967</v>
       </c>
       <c r="B182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>12539</v>
+        <v>11969</v>
       </c>
       <c r="B183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C183">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>12596</v>
+        <v>12058</v>
       </c>
       <c r="B184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C184">
-        <v>31</v>
+        <v>176</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>12616</v>
+        <v>12059</v>
       </c>
       <c r="B185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C185">
-        <v>41</v>
+        <v>176</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>12621</v>
+        <v>12128</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>12764</v>
+        <v>12139</v>
       </c>
       <c r="B187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C187">
-        <v>454</v>
+        <v>81</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>12870</v>
+        <v>12146</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>12907</v>
+        <v>12147</v>
       </c>
       <c r="B189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C189">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>12923</v>
+        <v>12270</v>
       </c>
       <c r="B190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C190">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>13028</v>
+        <v>12271</v>
       </c>
       <c r="B191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191">
-        <v>118</v>
+        <v>41</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>13034</v>
+        <v>12304</v>
       </c>
       <c r="B192">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C192">
-        <v>728</v>
+        <v>67</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>13249</v>
+        <v>12535</v>
       </c>
       <c r="B193">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C193">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>13258</v>
+        <v>12539</v>
       </c>
       <c r="B194">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C194">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>13266</v>
+        <v>12621</v>
       </c>
       <c r="B195">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C195">
-        <v>66</v>
+        <v>140</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>13269</v>
+        <v>12662</v>
       </c>
       <c r="B196">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C196">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>13283</v>
+        <v>12764</v>
       </c>
       <c r="B197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C197">
-        <v>189</v>
+        <v>453</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>13403</v>
+        <v>13023</v>
       </c>
       <c r="B198">
         <v>3</v>
       </c>
       <c r="C198">
-        <v>91</v>
+        <v>351</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>13417</v>
+        <v>13028</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C199">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>14037</v>
+        <v>13249</v>
       </c>
       <c r="B200">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C200">
-        <v>207</v>
+        <v>78</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>19685</v>
+        <v>13258</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C201">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>19924</v>
+        <v>13260</v>
       </c>
       <c r="B202">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C202">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>19971</v>
+        <v>13269</v>
       </c>
       <c r="B203">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C203">
-        <v>229</v>
+        <v>47</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>19981</v>
+        <v>13403</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>19982</v>
+        <v>14037</v>
       </c>
       <c r="B205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C205">
-        <v>35</v>
+        <v>207</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>19987</v>
+        <v>19685</v>
       </c>
       <c r="B206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C206">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>19988</v>
+        <v>19924</v>
       </c>
       <c r="B207">
         <v>2</v>
       </c>
       <c r="C207">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>20486</v>
+        <v>19968</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C208">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>20498</v>
+        <v>19982</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209">
-        <v>117</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>20555</v>
+        <v>19987</v>
       </c>
       <c r="B210">
         <v>2</v>
       </c>
       <c r="C210">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>20556</v>
+        <v>19988</v>
       </c>
       <c r="B211">
         <v>2</v>
       </c>
       <c r="C211">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>20650</v>
+        <v>20486</v>
       </c>
       <c r="B212">
         <v>1</v>
       </c>
       <c r="C212">
-        <v>141</v>
+        <v>83</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>20927</v>
+        <v>20555</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>20984</v>
+        <v>20650</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>21068</v>
+        <v>20927</v>
       </c>
       <c r="B215">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C215">
-        <v>328</v>
+        <v>48</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>21088</v>
+        <v>21068</v>
       </c>
       <c r="B216">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C216">
-        <v>7</v>
+        <v>316</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>21454</v>
+        <v>21088</v>
       </c>
       <c r="B217">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C217">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>21793</v>
+        <v>21454</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>21946</v>
+        <v>22313</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>22313</v>
+        <v>22317</v>
       </c>
       <c r="B220">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C220">
-        <v>41</v>
+        <v>250</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -2811,78 +2811,78 @@
         <v>10</v>
       </c>
       <c r="C221">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>22565</v>
+        <v>22573</v>
       </c>
       <c r="B222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C222">
-        <v>699</v>
+        <v>46</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>22573</v>
+        <v>22631</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C223">
-        <v>47</v>
+        <v>447</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>22631</v>
+        <v>22665</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C224">
-        <v>448</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>22665</v>
+        <v>23238</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C225">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>23489</v>
+        <v>23380</v>
       </c>
       <c r="B226">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C226">
-        <v>126</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>23491</v>
+        <v>23489</v>
       </c>
       <c r="B227">
         <v>3</v>
       </c>
       <c r="C227">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>23492</v>
+        <v>23491</v>
       </c>
       <c r="B228">
         <v>3</v>
@@ -2899,204 +2899,149 @@
         <v>3</v>
       </c>
       <c r="C229">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>23494</v>
+        <v>23992</v>
       </c>
       <c r="B230">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C230">
-        <v>127</v>
+        <v>25</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>23526</v>
+        <v>24126</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C231">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>23611</v>
+        <v>24127</v>
       </c>
       <c r="B232">
         <v>3</v>
       </c>
       <c r="C232">
-        <v>405</v>
+        <v>145</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>23992</v>
+        <v>24252</v>
       </c>
       <c r="B233">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>23994</v>
+        <v>24253</v>
       </c>
       <c r="B234">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C234">
-        <v>45</v>
+        <v>117</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>24125</v>
+        <v>24258</v>
       </c>
       <c r="B235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C235">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>24252</v>
+        <v>24707</v>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C236">
-        <v>7</v>
+        <v>739</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>24253</v>
+        <v>25278</v>
       </c>
       <c r="B237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C237">
-        <v>116</v>
+        <v>338</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>24256</v>
+        <v>25286</v>
       </c>
       <c r="B238">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>24260</v>
+        <v>25342</v>
       </c>
       <c r="B239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C239">
-        <v>168</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>24567</v>
+        <v>25344</v>
       </c>
       <c r="B240">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C240">
-        <v>184</v>
+        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>24705</v>
+        <v>26103</v>
       </c>
       <c r="B241">
         <v>2</v>
       </c>
       <c r="C241">
-        <v>258</v>
+        <v>54</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>25254</v>
+        <v>26229</v>
       </c>
       <c r="B242">
         <v>3</v>
       </c>
       <c r="C242">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
-      <c r="A243">
-        <v>25286</v>
-      </c>
-      <c r="B243">
-        <v>1</v>
-      </c>
-      <c r="C243">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
-        <v>25342</v>
-      </c>
-      <c r="B244">
-        <v>3</v>
-      </c>
-      <c r="C244">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245">
-        <v>25344</v>
-      </c>
-      <c r="B245">
-        <v>3</v>
-      </c>
-      <c r="C245">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246">
-        <v>26103</v>
-      </c>
-      <c r="B246">
-        <v>2</v>
-      </c>
-      <c r="C246">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247">
-        <v>26229</v>
-      </c>
-      <c r="B247">
-        <v>3</v>
-      </c>
-      <c r="C247">
         <v>7</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C242"/>
+  <dimension ref="A1:C229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,24 +396,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -429,156 +429,156 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>69</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>133</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>52</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>173</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>407</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>48</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>457</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18">
         <v>11</v>
       </c>
       <c r="C18">
-        <v>314</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -600,40 +600,40 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>93</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>186</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -644,320 +644,320 @@
         <v>2</v>
       </c>
       <c r="C24">
-        <v>186</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>901</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>442</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29">
-        <v>135</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30">
-        <v>478</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>423</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32">
-        <v>901</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>205</v>
+        <v>308</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>202</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>383</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>346</v>
+        <v>413</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>116</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>51</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>417</v>
+        <v>589</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>440</v>
+        <v>590</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>466</v>
+        <v>615</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>475</v>
+        <v>925</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>590</v>
+        <v>944</v>
       </c>
       <c r="B48">
         <v>15</v>
       </c>
       <c r="C48">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>593</v>
+        <v>949</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>139</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>615</v>
+        <v>965</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C50">
-        <v>59</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>624</v>
+        <v>972</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>62</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>823</v>
+        <v>974</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>903</v>
+        <v>1059</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -968,431 +968,431 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>922</v>
+        <v>1070</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>689</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>925</v>
+        <v>1082</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>926</v>
+        <v>1087</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>944</v>
+        <v>1126</v>
       </c>
       <c r="B57">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>27</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>947</v>
+        <v>1309</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>25</v>
+        <v>397</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>955</v>
+        <v>1413</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C59">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>965</v>
+        <v>1414</v>
       </c>
       <c r="B60">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>358</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>974</v>
+        <v>1447</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>118</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>990</v>
+        <v>1490</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>32</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>998</v>
+        <v>1599</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1080</v>
+        <v>1604</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C64">
-        <v>165</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1087</v>
+        <v>1622</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>166</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1091</v>
+        <v>1776</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>36</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>1124</v>
+        <v>2049</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>109</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>1163</v>
+        <v>2050</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68">
-        <v>210</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1309</v>
+        <v>2054</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>33</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1309</v>
+        <v>2055</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>397</v>
+        <v>281</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1407</v>
+        <v>2057</v>
       </c>
       <c r="B71">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>76</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1414</v>
+        <v>2104</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>61</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1447</v>
+        <v>2105</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>23</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1448</v>
+        <v>2109</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1599</v>
+        <v>2328</v>
       </c>
       <c r="B75">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>81</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>1622</v>
+        <v>2422</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C76">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2049</v>
+        <v>2423</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>331</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2109</v>
+        <v>2424</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2328</v>
+        <v>2436</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2335</v>
+        <v>2438</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>122</v>
+        <v>764</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2423</v>
+        <v>2538</v>
       </c>
       <c r="B81">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>224</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2424</v>
+        <v>2726</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>208</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2436</v>
+        <v>2728</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2438</v>
+        <v>2878</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>501</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2878</v>
+        <v>2911</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2879</v>
+        <v>2912</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2911</v>
+        <v>2916</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2912</v>
+        <v>2991</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>29</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2916</v>
+        <v>3016</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C89">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2934</v>
+        <v>3048</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2991</v>
+        <v>3258</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>177</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>3257</v>
+        <v>3429</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>94</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1425,7 +1425,7 @@
         <v>2</v>
       </c>
       <c r="C95">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1436,18 +1436,18 @@
         <v>3</v>
       </c>
       <c r="C96">
-        <v>24</v>
+        <v>794</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3898</v>
+        <v>3961</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1458,166 +1458,166 @@
         <v>2</v>
       </c>
       <c r="C98">
-        <v>139</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>4867</v>
+        <v>4901</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C99">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>4901</v>
+        <v>5005</v>
       </c>
       <c r="B100">
-        <v>332</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>4967</v>
+        <v>5083</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>5083</v>
+        <v>5152</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>5085</v>
+        <v>5165</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>5152</v>
+        <v>5343</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C104">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>5165</v>
+        <v>5343</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C105">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>5208</v>
+        <v>5490</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>339</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>5343</v>
+        <v>5494</v>
       </c>
       <c r="B107">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>5453</v>
+        <v>5513</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>79</v>
+        <v>47</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5490</v>
+        <v>5647</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>5494</v>
+        <v>5650</v>
       </c>
       <c r="B110">
         <v>2</v>
       </c>
       <c r="C110">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5577</v>
+        <v>5652</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>132</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5584</v>
+        <v>5654</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>157</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5646</v>
+        <v>5656</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -1628,1143 +1628,1143 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5647</v>
+        <v>5660</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5650</v>
+        <v>5723</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5652</v>
+        <v>5729</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>5654</v>
+        <v>6097</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C117">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>5656</v>
+        <v>6097</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C118">
-        <v>34</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>5660</v>
+        <v>6098</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C119">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>5723</v>
+        <v>6158</v>
       </c>
       <c r="B120">
         <v>2</v>
       </c>
       <c r="C120">
-        <v>38</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>5729</v>
+        <v>6540</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C121">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>6097</v>
+        <v>6935</v>
       </c>
       <c r="B122">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C122">
-        <v>21</v>
+        <v>160</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>6097</v>
+        <v>6936</v>
       </c>
       <c r="B123">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>83</v>
+        <v>316</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>6098</v>
+        <v>7084</v>
       </c>
       <c r="B124">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>6540</v>
+        <v>7520</v>
       </c>
       <c r="B125">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>92</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>6952</v>
+        <v>7885</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C126">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>7004</v>
+        <v>7886</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C127">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>7005</v>
+        <v>7887</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>48</v>
+        <v>167</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>7084</v>
+        <v>8055</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C129">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>7457</v>
+        <v>8104</v>
       </c>
       <c r="B130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>7520</v>
+        <v>8120</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>12</v>
+        <v>281</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>7558</v>
+        <v>8121</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>39</v>
+        <v>178</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>7567</v>
+        <v>8216</v>
       </c>
       <c r="B133">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>8055</v>
+        <v>8216</v>
       </c>
       <c r="B134">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>8104</v>
+        <v>8283</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>287</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>8157</v>
+        <v>8285</v>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>25</v>
+        <v>283</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>8216</v>
+        <v>8286</v>
       </c>
       <c r="B137">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>1277</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>8274</v>
+        <v>8635</v>
       </c>
       <c r="B138">
         <v>3</v>
       </c>
       <c r="C138">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>8283</v>
+        <v>8650</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>303</v>
+        <v>220</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>8284</v>
+        <v>8672</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>303</v>
+        <v>338</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>8285</v>
+        <v>8674</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>303</v>
+        <v>167</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>8286</v>
+        <v>8675</v>
       </c>
       <c r="B142">
         <v>2</v>
       </c>
       <c r="C142">
-        <v>303</v>
+        <v>222</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8672</v>
+        <v>8676</v>
       </c>
       <c r="B143">
         <v>2</v>
       </c>
       <c r="C143">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8674</v>
+        <v>8990</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C144">
-        <v>225</v>
+        <v>65</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>8676</v>
+        <v>9065</v>
       </c>
       <c r="B145">
         <v>2</v>
       </c>
       <c r="C145">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>8853</v>
+        <v>9068</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>325</v>
+        <v>77</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>8945</v>
+        <v>9081</v>
       </c>
       <c r="B147">
         <v>3</v>
       </c>
       <c r="C147">
-        <v>468</v>
+        <v>583</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>8990</v>
+        <v>9087</v>
       </c>
       <c r="B148">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>9065</v>
+        <v>9507</v>
       </c>
       <c r="B149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>191</v>
+        <v>124</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>9068</v>
+        <v>9760</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C150">
-        <v>76</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>9069</v>
+        <v>9827</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>9070</v>
+        <v>10149</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>39</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>9081</v>
+        <v>10172</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>583</v>
+        <v>99</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>9087</v>
+        <v>10172</v>
       </c>
       <c r="B154">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>87</v>
+        <v>986</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>9289</v>
+        <v>10524</v>
       </c>
       <c r="B155">
         <v>29</v>
       </c>
       <c r="C155">
-        <v>115</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>9357</v>
+        <v>10527</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>28</v>
+        <v>562</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>9608</v>
+        <v>10529</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C157">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>9613</v>
+        <v>10530</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C158">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>9829</v>
+        <v>10574</v>
       </c>
       <c r="B159">
         <v>3</v>
       </c>
       <c r="C159">
-        <v>85</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>9833</v>
+        <v>10719</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C160">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>9960</v>
+        <v>10780</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C161">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>10170</v>
+        <v>10825</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C162">
-        <v>33</v>
+        <v>794</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>10524</v>
+        <v>11039</v>
       </c>
       <c r="B163">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C163">
-        <v>33</v>
+        <v>120</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>10529</v>
+        <v>11081</v>
       </c>
       <c r="B164">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C164">
-        <v>50</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>10530</v>
+        <v>11085</v>
       </c>
       <c r="B165">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C165">
-        <v>30</v>
+        <v>332</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>10719</v>
+        <v>11116</v>
       </c>
       <c r="B166">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>10816</v>
+        <v>11396</v>
       </c>
       <c r="B167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C167">
-        <v>408</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>10825</v>
+        <v>11492</v>
       </c>
       <c r="B168">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C168">
-        <v>411</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>11116</v>
+        <v>11493</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>11150</v>
+        <v>11504</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170">
-        <v>27</v>
+        <v>83</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>11492</v>
+        <v>11510</v>
       </c>
       <c r="B171">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>56</v>
+        <v>362</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>11493</v>
+        <v>11690</v>
       </c>
       <c r="B172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C172">
-        <v>26</v>
+        <v>184</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>11687</v>
+        <v>11737</v>
       </c>
       <c r="B173">
         <v>2</v>
       </c>
       <c r="C173">
-        <v>191</v>
+        <v>35</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>11689</v>
+        <v>11785</v>
       </c>
       <c r="B174">
         <v>2</v>
       </c>
       <c r="C174">
-        <v>191</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>11711</v>
+        <v>11794</v>
       </c>
       <c r="B175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>11738</v>
+        <v>11952</v>
       </c>
       <c r="B176">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11739</v>
+        <v>11961</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11794</v>
+        <v>11962</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11848</v>
+        <v>11967</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>171</v>
+        <v>80</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11895</v>
+        <v>11969</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>11962</v>
+        <v>12010</v>
       </c>
       <c r="B181">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C181">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>11967</v>
+        <v>12128</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>11969</v>
+        <v>12147</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>12058</v>
+        <v>12304</v>
       </c>
       <c r="B184">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184">
-        <v>176</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>12059</v>
+        <v>12535</v>
       </c>
       <c r="B185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185">
-        <v>176</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>12128</v>
+        <v>12539</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>12139</v>
+        <v>12607</v>
       </c>
       <c r="B187">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C187">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>12146</v>
+        <v>12662</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>12147</v>
+        <v>12721</v>
       </c>
       <c r="B189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189">
-        <v>54</v>
+        <v>335</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>12270</v>
+        <v>12764</v>
       </c>
       <c r="B190">
         <v>2</v>
       </c>
       <c r="C190">
-        <v>7</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>12271</v>
+        <v>12870</v>
       </c>
       <c r="B191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191">
-        <v>41</v>
+        <v>167</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>12304</v>
+        <v>13023</v>
       </c>
       <c r="B192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C192">
-        <v>67</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>12535</v>
+        <v>13028</v>
       </c>
       <c r="B193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C193">
-        <v>35</v>
+        <v>87</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>12539</v>
+        <v>13249</v>
       </c>
       <c r="B194">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C194">
-        <v>18</v>
+        <v>77</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>12621</v>
+        <v>13258</v>
       </c>
       <c r="B195">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C195">
-        <v>140</v>
+        <v>31</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>12662</v>
+        <v>13259</v>
       </c>
       <c r="B196">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C196">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>12764</v>
+        <v>13259</v>
       </c>
       <c r="B197">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C197">
-        <v>453</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>13023</v>
+        <v>13403</v>
       </c>
       <c r="B198">
         <v>3</v>
       </c>
       <c r="C198">
-        <v>351</v>
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>13028</v>
+        <v>13968</v>
       </c>
       <c r="B199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C199">
-        <v>87</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>13249</v>
+        <v>14037</v>
       </c>
       <c r="B200">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C200">
-        <v>78</v>
+        <v>208</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>13258</v>
+        <v>19982</v>
       </c>
       <c r="B201">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C201">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>13260</v>
+        <v>19988</v>
       </c>
       <c r="B202">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C202">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>13269</v>
+        <v>20486</v>
       </c>
       <c r="B203">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C203">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>13403</v>
+        <v>20555</v>
       </c>
       <c r="B204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C204">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>14037</v>
+        <v>21068</v>
       </c>
       <c r="B205">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C205">
-        <v>207</v>
+        <v>311</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>19685</v>
+        <v>21088</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C206">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>19924</v>
+        <v>21454</v>
       </c>
       <c r="B207">
         <v>2</v>
       </c>
       <c r="C207">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>19968</v>
+        <v>21793</v>
       </c>
       <c r="B208">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C208">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>19982</v>
+        <v>22313</v>
       </c>
       <c r="B209">
         <v>2</v>
       </c>
       <c r="C209">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>19987</v>
+        <v>22554</v>
       </c>
       <c r="B210">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C210">
-        <v>38</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>19988</v>
+        <v>22565</v>
       </c>
       <c r="B211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C211">
-        <v>45</v>
+        <v>703</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>20486</v>
+        <v>22573</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212">
-        <v>83</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>20555</v>
+        <v>22631</v>
       </c>
       <c r="B213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C213">
-        <v>36</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>20650</v>
+        <v>23493</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>20927</v>
+        <v>23611</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C215">
-        <v>48</v>
+        <v>270</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>21068</v>
+        <v>23992</v>
       </c>
       <c r="B216">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C216">
-        <v>316</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>21088</v>
+        <v>24127</v>
       </c>
       <c r="B217">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C217">
         <v>7</v>
@@ -2772,276 +2772,133 @@
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>21454</v>
+        <v>24252</v>
       </c>
       <c r="B218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>22313</v>
+        <v>24257</v>
       </c>
       <c r="B219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>22317</v>
+        <v>24260</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C220">
-        <v>250</v>
+        <v>112</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>22554</v>
+        <v>24566</v>
       </c>
       <c r="B221">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>446</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>22573</v>
+        <v>24705</v>
       </c>
       <c r="B222">
         <v>2</v>
       </c>
       <c r="C222">
-        <v>46</v>
+        <v>216</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>22631</v>
+        <v>24707</v>
       </c>
       <c r="B223">
         <v>3</v>
       </c>
       <c r="C223">
-        <v>447</v>
+        <v>736</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>22665</v>
+        <v>25286</v>
       </c>
       <c r="B224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>23238</v>
+        <v>25342</v>
       </c>
       <c r="B225">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C225">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>23380</v>
+        <v>25344</v>
       </c>
       <c r="B226">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C226">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>23489</v>
+        <v>25899</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
-        <v>126</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>23491</v>
+        <v>26103</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C228">
-        <v>129</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>23493</v>
+        <v>26229</v>
       </c>
       <c r="B229">
         <v>3</v>
       </c>
       <c r="C229">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230">
-        <v>23992</v>
-      </c>
-      <c r="B230">
-        <v>29</v>
-      </c>
-      <c r="C230">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231">
-        <v>24126</v>
-      </c>
-      <c r="B231">
-        <v>3</v>
-      </c>
-      <c r="C231">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232">
-        <v>24127</v>
-      </c>
-      <c r="B232">
-        <v>3</v>
-      </c>
-      <c r="C232">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233">
-        <v>24252</v>
-      </c>
-      <c r="B233">
-        <v>1</v>
-      </c>
-      <c r="C233">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234">
-        <v>24253</v>
-      </c>
-      <c r="B234">
-        <v>1</v>
-      </c>
-      <c r="C234">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
-      <c r="A235">
-        <v>24258</v>
-      </c>
-      <c r="B235">
-        <v>1</v>
-      </c>
-      <c r="C235">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
-      <c r="A236">
-        <v>24707</v>
-      </c>
-      <c r="B236">
-        <v>3</v>
-      </c>
-      <c r="C236">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
-      <c r="A237">
-        <v>25278</v>
-      </c>
-      <c r="B237">
-        <v>2</v>
-      </c>
-      <c r="C237">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
-      <c r="A238">
-        <v>25286</v>
-      </c>
-      <c r="B238">
-        <v>1</v>
-      </c>
-      <c r="C238">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239">
-        <v>25342</v>
-      </c>
-      <c r="B239">
-        <v>3</v>
-      </c>
-      <c r="C239">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240">
-        <v>25344</v>
-      </c>
-      <c r="B240">
-        <v>3</v>
-      </c>
-      <c r="C240">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241">
-        <v>26103</v>
-      </c>
-      <c r="B241">
-        <v>2</v>
-      </c>
-      <c r="C241">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242">
-        <v>26229</v>
-      </c>
-      <c r="B242">
-        <v>3</v>
-      </c>
-      <c r="C242">
         <v>7</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_701.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,62 +396,62 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>73</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>132</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -473,150 +473,150 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>205</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>91</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>135</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>339</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>73</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>859</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>513</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>210</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -627,79 +627,79 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>91</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>180</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>39</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>442</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>135</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29">
-        <v>241</v>
+        <v>901</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -710,103 +710,103 @@
         <v>3</v>
       </c>
       <c r="C30">
-        <v>447</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>397</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>88</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>308</v>
+        <v>216</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>101</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>345</v>
+        <v>248</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>383</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>411</v>
+        <v>332</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38">
-        <v>64</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>413</v>
+        <v>334</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C39">
         <v>51</v>
@@ -814,508 +814,508 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>51</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>417</v>
+        <v>346</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>491</v>
+        <v>361</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>273</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>589</v>
+        <v>409</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>590</v>
+        <v>412</v>
       </c>
       <c r="B45">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>615</v>
+        <v>413</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>925</v>
+        <v>414</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>33</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>944</v>
+        <v>415</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>949</v>
+        <v>434</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>965</v>
+        <v>475</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>370</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>972</v>
+        <v>491</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>364</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>974</v>
+        <v>589</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>92</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>1059</v>
+        <v>823</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>1070</v>
+        <v>903</v>
       </c>
       <c r="B54">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>689</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>1082</v>
+        <v>925</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>1087</v>
+        <v>944</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>1126</v>
+        <v>949</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C57">
-        <v>270</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>1309</v>
+        <v>952</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>397</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>1413</v>
+        <v>955</v>
       </c>
       <c r="B59">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>1414</v>
+        <v>956</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>61</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1447</v>
+        <v>957</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1490</v>
+        <v>965</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>66</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1599</v>
+        <v>996</v>
       </c>
       <c r="B63">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>197</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>1604</v>
+        <v>1070</v>
       </c>
       <c r="B64">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>682</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>1622</v>
+        <v>1082</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>1776</v>
+        <v>1309</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>174</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2049</v>
+        <v>1413</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>331</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2050</v>
+        <v>1414</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C68">
-        <v>284</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2054</v>
+        <v>1447</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>281</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2055</v>
+        <v>1490</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>281</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2057</v>
+        <v>1599</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C71">
-        <v>281</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2104</v>
+        <v>1604</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C72">
-        <v>202</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2105</v>
+        <v>1622</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>176</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2109</v>
+        <v>1776</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2328</v>
+        <v>1777</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>156</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2422</v>
+        <v>1801</v>
       </c>
       <c r="B76">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>112</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2423</v>
+        <v>2188</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>224</v>
+        <v>485</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="B78">
         <v>80</v>
       </c>
       <c r="C78">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2436</v>
+        <v>2423</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C79">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2438</v>
+        <v>2424</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C80">
-        <v>764</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2538</v>
+        <v>2436</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C81">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2726</v>
+        <v>2438</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>764</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2728</v>
+        <v>2538</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2878</v>
+        <v>2703</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>89</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2911</v>
+        <v>2729</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1342,32 +1342,32 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2991</v>
+        <v>3016</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C88">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>3016</v>
+        <v>3048</v>
       </c>
       <c r="B89">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>30</v>
+        <v>325</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>3048</v>
+        <v>3257</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -1419,109 +1419,109 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>3478</v>
+        <v>3462</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>3495</v>
+        <v>3475</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>794</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>3961</v>
+        <v>3495</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>37</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>4246</v>
+        <v>3899</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>4901</v>
+        <v>4019</v>
       </c>
       <c r="B99">
-        <v>332</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>5005</v>
+        <v>4043</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>5083</v>
+        <v>4246</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>5152</v>
+        <v>4867</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>5165</v>
+        <v>4901</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="C103">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>5343</v>
+        <v>5005</v>
       </c>
       <c r="B104">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -1529,626 +1529,626 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>5343</v>
+        <v>5080</v>
       </c>
       <c r="B105">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>5490</v>
+        <v>5081</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>5494</v>
+        <v>5083</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>5513</v>
+        <v>5152</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>5647</v>
+        <v>5153</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>5650</v>
+        <v>5165</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>5652</v>
+        <v>5208</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>5654</v>
+        <v>5343</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C112">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>5656</v>
+        <v>5343</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C113">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>5660</v>
+        <v>5452</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>5723</v>
+        <v>5490</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>5729</v>
+        <v>5491</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>61</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>6097</v>
+        <v>5493</v>
       </c>
       <c r="B117">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>6097</v>
+        <v>5494</v>
       </c>
       <c r="B118">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>6098</v>
+        <v>5513</v>
       </c>
       <c r="B119">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>6158</v>
+        <v>5646</v>
       </c>
       <c r="B120">
         <v>2</v>
       </c>
       <c r="C120">
-        <v>209</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>6540</v>
+        <v>5647</v>
       </c>
       <c r="B121">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>92</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>6935</v>
+        <v>5650</v>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>160</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>6936</v>
+        <v>5652</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>316</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>7084</v>
+        <v>5654</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>7520</v>
+        <v>5656</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>7885</v>
+        <v>5723</v>
       </c>
       <c r="B126">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>84</v>
+        <v>37</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>7886</v>
+        <v>5729</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C127">
-        <v>86</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>7887</v>
+        <v>6097</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C128">
-        <v>167</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>8055</v>
+        <v>6097</v>
       </c>
       <c r="B129">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>8104</v>
+        <v>6098</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>8120</v>
+        <v>6497</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>281</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>8121</v>
+        <v>6540</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>178</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>8216</v>
+        <v>6935</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>53</v>
+        <v>160</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>8216</v>
+        <v>7084</v>
       </c>
       <c r="B134">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>1277</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>8283</v>
+        <v>7324</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>287</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>8285</v>
+        <v>7520</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>283</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>8286</v>
+        <v>7707</v>
       </c>
       <c r="B137">
         <v>2</v>
       </c>
       <c r="C137">
-        <v>580</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>8635</v>
+        <v>7885</v>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>8650</v>
+        <v>7886</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C139">
-        <v>220</v>
+        <v>86</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>8672</v>
+        <v>7887</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C140">
-        <v>338</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>8674</v>
+        <v>8055</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>167</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>8675</v>
+        <v>8104</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>222</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>8676</v>
+        <v>8120</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>168</v>
+        <v>281</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>8990</v>
+        <v>8284</v>
       </c>
       <c r="B144">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>65</v>
+        <v>286</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>9065</v>
+        <v>8285</v>
       </c>
       <c r="B145">
         <v>2</v>
       </c>
       <c r="C145">
-        <v>183</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>9068</v>
+        <v>8648</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>9081</v>
+        <v>8651</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>583</v>
+        <v>109</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>9087</v>
+        <v>8675</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>44</v>
+        <v>335</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>9507</v>
+        <v>8938</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>124</v>
+        <v>219</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>9760</v>
+        <v>8939</v>
       </c>
       <c r="B150">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>41</v>
+        <v>96</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>9827</v>
+        <v>8990</v>
       </c>
       <c r="B151">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>10149</v>
+        <v>9065</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C152">
-        <v>1499</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>10172</v>
+        <v>9068</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>10172</v>
+        <v>9081</v>
       </c>
       <c r="B154">
         <v>3</v>
       </c>
       <c r="C154">
-        <v>986</v>
+        <v>580</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>10524</v>
+        <v>9209</v>
       </c>
       <c r="B155">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C155">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>10527</v>
+        <v>9357</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>562</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>10529</v>
+        <v>9507</v>
       </c>
       <c r="B157">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>33</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>10530</v>
+        <v>9608</v>
       </c>
       <c r="B158">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>10574</v>
+        <v>9783</v>
       </c>
       <c r="B159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>8</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>10719</v>
+        <v>9827</v>
       </c>
       <c r="B160">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="C160">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>10780</v>
+        <v>9829</v>
       </c>
       <c r="B161">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -2156,560 +2156,560 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>10825</v>
+        <v>9833</v>
       </c>
       <c r="B162">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C162">
-        <v>794</v>
+        <v>76</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>11039</v>
+        <v>10149</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163">
-        <v>120</v>
+        <v>567</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>11081</v>
+        <v>10172</v>
       </c>
       <c r="B164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>426</v>
+        <v>99</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>11085</v>
+        <v>10524</v>
       </c>
       <c r="B165">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C165">
-        <v>332</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>11116</v>
+        <v>10527</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C166">
-        <v>48</v>
+        <v>567</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>11396</v>
+        <v>10529</v>
       </c>
       <c r="B167">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C167">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>11492</v>
+        <v>10530</v>
       </c>
       <c r="B168">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C168">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>11493</v>
+        <v>10717</v>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C169">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>11504</v>
+        <v>10719</v>
       </c>
       <c r="B170">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C170">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>11510</v>
+        <v>10780</v>
       </c>
       <c r="B171">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C171">
-        <v>362</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>11690</v>
+        <v>11399</v>
       </c>
       <c r="B172">
         <v>2</v>
       </c>
       <c r="C172">
-        <v>184</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>11737</v>
+        <v>11489</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>11785</v>
+        <v>11492</v>
       </c>
       <c r="B174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>11794</v>
+        <v>11493</v>
       </c>
       <c r="B175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C175">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>11952</v>
+        <v>11510</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C176">
-        <v>7</v>
+        <v>362</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>11961</v>
+        <v>11644</v>
       </c>
       <c r="B177">
         <v>1</v>
       </c>
       <c r="C177">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>11962</v>
+        <v>11689</v>
       </c>
       <c r="B178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178">
-        <v>52</v>
+        <v>363</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>11967</v>
+        <v>11794</v>
       </c>
       <c r="B179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>11969</v>
+        <v>11895</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>12010</v>
+        <v>11962</v>
       </c>
       <c r="B181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C181">
-        <v>96</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>12128</v>
+        <v>11967</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>12147</v>
+        <v>11969</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>12304</v>
+        <v>12128</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>12535</v>
+        <v>12269</v>
       </c>
       <c r="B185">
         <v>2</v>
       </c>
       <c r="C185">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>12539</v>
+        <v>12270</v>
       </c>
       <c r="B186">
         <v>2</v>
       </c>
       <c r="C186">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>12607</v>
+        <v>12271</v>
       </c>
       <c r="B187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187">
-        <v>95</v>
+        <v>41</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>12662</v>
+        <v>12535</v>
       </c>
       <c r="B188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C188">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>12721</v>
+        <v>12539</v>
       </c>
       <c r="B189">
         <v>2</v>
       </c>
       <c r="C189">
-        <v>335</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>12764</v>
+        <v>12607</v>
       </c>
       <c r="B190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C190">
-        <v>453</v>
+        <v>95</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>12870</v>
+        <v>12621</v>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>167</v>
+        <v>234</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>13023</v>
+        <v>12661</v>
       </c>
       <c r="B192">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C192">
-        <v>1177</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>13028</v>
+        <v>12662</v>
       </c>
       <c r="B193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C193">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>13249</v>
+        <v>12676</v>
       </c>
       <c r="B194">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C194">
-        <v>77</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>13258</v>
+        <v>12764</v>
       </c>
       <c r="B195">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C195">
-        <v>31</v>
+        <v>456</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>13259</v>
+        <v>12791</v>
       </c>
       <c r="B196">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C196">
-        <v>42</v>
+        <v>481</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>13259</v>
+        <v>12870</v>
       </c>
       <c r="B197">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C197">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>13403</v>
+        <v>12925</v>
       </c>
       <c r="B198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C198">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>13968</v>
+        <v>13249</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C199">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>14037</v>
+        <v>13258</v>
       </c>
       <c r="B200">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C200">
-        <v>208</v>
+        <v>31</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>19982</v>
+        <v>13259</v>
       </c>
       <c r="B201">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C201">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>19988</v>
+        <v>13403</v>
       </c>
       <c r="B202">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C202">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>20486</v>
+        <v>13488</v>
       </c>
       <c r="B203">
         <v>1</v>
       </c>
       <c r="C203">
-        <v>83</v>
+        <v>144</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>20555</v>
+        <v>13968</v>
       </c>
       <c r="B204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C204">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>21068</v>
+        <v>14038</v>
       </c>
       <c r="B205">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C205">
-        <v>311</v>
+        <v>218</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>21088</v>
+        <v>19980</v>
       </c>
       <c r="B206">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>21454</v>
+        <v>19981</v>
       </c>
       <c r="B207">
         <v>2</v>
       </c>
       <c r="C207">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>21793</v>
+        <v>19982</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C208">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>22313</v>
+        <v>19987</v>
       </c>
       <c r="B209">
         <v>2</v>
       </c>
       <c r="C209">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>22554</v>
+        <v>19988</v>
       </c>
       <c r="B210">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C210">
-        <v>440</v>
+        <v>69</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>22565</v>
+        <v>20555</v>
       </c>
       <c r="B211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211">
-        <v>703</v>
+        <v>36</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>22573</v>
+        <v>20650</v>
       </c>
       <c r="B212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C212">
         <v>7</v>
@@ -2717,189 +2717,354 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>22631</v>
+        <v>21068</v>
       </c>
       <c r="B213">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>447</v>
+        <v>310</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>23493</v>
+        <v>21088</v>
       </c>
       <c r="B214">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C214">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>23611</v>
+        <v>21454</v>
       </c>
       <c r="B215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215">
-        <v>270</v>
+        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>23992</v>
+        <v>21793</v>
       </c>
       <c r="B216">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C216">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>24127</v>
+        <v>21946</v>
       </c>
       <c r="B217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C217">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>24252</v>
+        <v>22089</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C218">
-        <v>7</v>
+        <v>126</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>24257</v>
+        <v>22313</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C219">
-        <v>165</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>24260</v>
+        <v>22316</v>
       </c>
       <c r="B220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C220">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>24566</v>
+        <v>22554</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C221">
-        <v>7</v>
+        <v>442</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>24705</v>
+        <v>22558</v>
       </c>
       <c r="B222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C222">
-        <v>216</v>
+        <v>293</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>24707</v>
+        <v>22565</v>
       </c>
       <c r="B223">
         <v>3</v>
       </c>
       <c r="C223">
-        <v>736</v>
+        <v>351</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>25286</v>
+        <v>22631</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C224">
-        <v>49</v>
+        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>25342</v>
+        <v>23380</v>
       </c>
       <c r="B225">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C225">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>25344</v>
+        <v>23489</v>
       </c>
       <c r="B226">
         <v>3</v>
       </c>
       <c r="C226">
-        <v>80</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>25899</v>
+        <v>23493</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C227">
-        <v>8</v>
+        <v>129</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>26103</v>
+        <v>23992</v>
       </c>
       <c r="B228">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C228">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
+        <v>24126</v>
+      </c>
+      <c r="B229">
+        <v>3</v>
+      </c>
+      <c r="C229">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230">
+        <v>24127</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231">
+        <v>24252</v>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232">
+        <v>24257</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233">
+        <v>24258</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234">
+        <v>24260</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235">
+        <v>24566</v>
+      </c>
+      <c r="B235">
+        <v>1</v>
+      </c>
+      <c r="C235">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <v>24705</v>
+      </c>
+      <c r="B236">
+        <v>2</v>
+      </c>
+      <c r="C236">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <v>24707</v>
+      </c>
+      <c r="B237">
+        <v>3</v>
+      </c>
+      <c r="C237">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <v>25286</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <v>25342</v>
+      </c>
+      <c r="B239">
+        <v>3</v>
+      </c>
+      <c r="C239">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>25344</v>
+      </c>
+      <c r="B240">
+        <v>3</v>
+      </c>
+      <c r="C240">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <v>25345</v>
+      </c>
+      <c r="B241">
+        <v>3</v>
+      </c>
+      <c r="C241">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <v>25899</v>
+      </c>
+      <c r="B242">
+        <v>2</v>
+      </c>
+      <c r="C242">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <v>26103</v>
+      </c>
+      <c r="B243">
+        <v>2</v>
+      </c>
+      <c r="C243">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
         <v>26229</v>
       </c>
-      <c r="B229">
-        <v>3</v>
-      </c>
-      <c r="C229">
-        <v>7</v>
+      <c r="B244">
+        <v>3</v>
+      </c>
+      <c r="C244">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
